--- a/Ranking_Data.xlsx
+++ b/Ranking_Data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="c:\Users\원영이\Desktop\ATL AUTO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B5AD2934-E729-4FEC-A5AD-083A529250BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{277E5AF0-DAE9-4784-8773-243B1D0DF7CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="314" yWindow="955" windowWidth="36185" windowHeight="19576" xr2:uid="{A471F9F2-EA72-4823-940B-F00855AE1D46}"/>
+    <workbookView xWindow="314" yWindow="955" windowWidth="36185" windowHeight="19576" xr2:uid="{766E9525-FD43-4413-8099-6C2895B4C4E6}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -731,7 +731,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CB89F0F8-3AAC-4BE7-A80D-216A40775E9E}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AC97F492-078C-430C-8C30-909A05F386F5}">
   <dimension ref="A1:Y29"/>
   <sheetFormatPr defaultRowHeight="15.7" x14ac:dyDescent="0.3"/>
   <sheetData>

--- a/Ranking_Data.xlsx
+++ b/Ranking_Data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="c:\Users\원영이\Desktop\ATL AUTO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{277E5AF0-DAE9-4784-8773-243B1D0DF7CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{926B95D7-CC23-4DE5-A4BC-195092CE60C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="314" yWindow="955" windowWidth="36185" windowHeight="19576" xr2:uid="{766E9525-FD43-4413-8099-6C2895B4C4E6}"/>
+    <workbookView xWindow="314" yWindow="955" windowWidth="36185" windowHeight="19576" xr2:uid="{0B284692-EF3A-4E3C-97E3-D2D5B039E418}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -731,7 +731,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AC97F492-078C-430C-8C30-909A05F386F5}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{87714EE8-F9C0-4E86-B6AA-D2C94CB42EDB}">
   <dimension ref="A1:Y29"/>
   <sheetFormatPr defaultRowHeight="15.7" x14ac:dyDescent="0.3"/>
   <sheetData>

--- a/Ranking_Data.xlsx
+++ b/Ranking_Data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="c:\Users\원영이\Desktop\ATL AUTO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{20541DAA-3827-4C35-A8E5-C1149149BDE3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{C5099787-44CE-41DB-8C2E-BA2E004333EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="314" yWindow="955" windowWidth="36185" windowHeight="19576" xr2:uid="{1D6FC72D-549F-4B7E-ADBB-74BD5CDCA9FA}"/>
+    <workbookView xWindow="314" yWindow="955" windowWidth="36185" windowHeight="19576" xr2:uid="{E082C765-AD56-4ACF-949A-3EA4052F1488}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -637,7 +637,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{27269916-11CE-4374-A763-F555C98AE6E6}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BBF8066C-7588-4994-881C-DFA5CBAE000B}">
   <dimension ref="A1:N29"/>
   <sheetFormatPr defaultRowHeight="15.7" x14ac:dyDescent="0.3"/>
   <sheetData>

--- a/Ranking_Data.xlsx
+++ b/Ranking_Data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="c:\Users\원영이\Desktop\ATL AUTO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C5099787-44CE-41DB-8C2E-BA2E004333EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{C0C1F079-8EC9-4916-93ED-B6334E3F0518}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="314" yWindow="955" windowWidth="36185" windowHeight="19576" xr2:uid="{E082C765-AD56-4ACF-949A-3EA4052F1488}"/>
+    <workbookView xWindow="314" yWindow="955" windowWidth="36185" windowHeight="19576" xr2:uid="{7FD324CC-1F2F-4F87-853F-C9D8FCD7DE16}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,11 +39,14 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="73">
   <si>
     <t>17th ELO</t>
   </si>
   <si>
+    <t>±</t>
+  </si>
+  <si>
     <t>닉네임</t>
   </si>
   <si>
@@ -68,31 +71,37 @@
     <t>바이에른 뮌헨</t>
   </si>
   <si>
+    <t>Legend독수리</t>
+  </si>
+  <si>
+    <t>17시즌</t>
+  </si>
+  <si>
+    <t>맨체스터 유나이티드</t>
+  </si>
+  <si>
+    <t>UNIT</t>
+  </si>
+  <si>
+    <t>AS 로마</t>
+  </si>
+  <si>
+    <t>대회종류</t>
+  </si>
+  <si>
+    <t>ELO 변동값</t>
+  </si>
+  <si>
+    <t>경기 수</t>
+  </si>
+  <si>
     <t>Voor</t>
   </si>
   <si>
-    <t>17시즌</t>
-  </si>
-  <si>
     <t>첼시</t>
   </si>
   <si>
-    <t>대회종류</t>
-  </si>
-  <si>
-    <t>ELO 변동값</t>
-  </si>
-  <si>
-    <t>경기 수</t>
-  </si>
-  <si>
-    <t>UNIT</t>
-  </si>
-  <si>
-    <t>AS 로마</t>
-  </si>
-  <si>
-    <t>1부리그</t>
+    <t>3부리그</t>
   </si>
   <si>
     <t>검정소</t>
@@ -110,7 +119,7 @@
     <t>아스널</t>
   </si>
   <si>
-    <t>UEFA_B조</t>
+    <t>UEFA_A조</t>
   </si>
   <si>
     <t>은안</t>
@@ -143,6 +152,12 @@
     <t>프랑크푸르트</t>
   </si>
   <si>
+    <t>호야국2인</t>
+  </si>
+  <si>
+    <t>SSC 나폴리</t>
+  </si>
+  <si>
     <t>ZD장인지참치</t>
   </si>
   <si>
@@ -155,42 +170,36 @@
     <t>아틀레티코 마드리드</t>
   </si>
   <si>
-    <t>호야국2인</t>
-  </si>
-  <si>
-    <t>SSC 나폴리</t>
-  </si>
-  <si>
     <t>방덕</t>
   </si>
   <si>
     <t>인테르</t>
   </si>
   <si>
+    <t>비주류중독</t>
+  </si>
+  <si>
+    <t>셀틱 FC</t>
+  </si>
+  <si>
+    <t>콩콩콩룔</t>
+  </si>
+  <si>
+    <t>라치오</t>
+  </si>
+  <si>
+    <t>여수가스</t>
+  </si>
+  <si>
+    <t>AS 모나코</t>
+  </si>
+  <si>
     <t>suma수마</t>
   </si>
   <si>
     <t>ACF 피오렌티나</t>
   </si>
   <si>
-    <t>여수가스</t>
-  </si>
-  <si>
-    <t>AS 모나코</t>
-  </si>
-  <si>
-    <t>콩콩콩룔</t>
-  </si>
-  <si>
-    <t>라치오</t>
-  </si>
-  <si>
-    <t>비주류중독</t>
-  </si>
-  <si>
-    <t>셀틱 FC</t>
-  </si>
-  <si>
     <t>Gucci와퍼</t>
   </si>
   <si>
@@ -215,18 +224,18 @@
     <t>레알 마드리드</t>
   </si>
   <si>
+    <t>용신</t>
+  </si>
+  <si>
+    <t>토트넘</t>
+  </si>
+  <si>
     <t>경남FC가즈아</t>
   </si>
   <si>
     <t>경남 FC</t>
   </si>
   <si>
-    <t>용신</t>
-  </si>
-  <si>
-    <t>토트넘</t>
-  </si>
-  <si>
     <t>A지냐크</t>
   </si>
   <si>
@@ -243,12 +252,6 @@
   </si>
   <si>
     <t>상하이 선화</t>
-  </si>
-  <si>
-    <t>Legend독수리</t>
-  </si>
-  <si>
-    <t>맨체스터 유나이티드</t>
   </si>
   <si>
     <t>겐지간지</t>
@@ -637,11 +640,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BBF8066C-7588-4994-881C-DFA5CBAE000B}">
-  <dimension ref="A1:N29"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{59BFAA15-8B7E-443F-9A3D-B8662BDD0CB7}">
+  <dimension ref="A1:O29"/>
   <sheetFormatPr defaultRowHeight="15.7" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -663,72 +666,78 @@
       <c r="G1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A2">
-        <v>1149.50125</v>
-      </c>
-      <c r="B2" t="s">
-        <v>7</v>
+        <v>1153.174</v>
+      </c>
+      <c r="B2">
+        <v>38.309999999999945</v>
       </c>
       <c r="C2" t="s">
         <v>8</v>
       </c>
-      <c r="D2">
-        <v>4</v>
+      <c r="D2" t="s">
+        <v>9</v>
       </c>
       <c r="E2">
         <v>4</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G2">
         <v>0</v>
       </c>
-      <c r="I2" t="s">
-        <v>9</v>
-      </c>
-      <c r="K2" t="s">
+      <c r="H2">
+        <v>0</v>
+      </c>
+      <c r="J2" t="s">
         <v>10</v>
       </c>
       <c r="L2" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="M2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A3">
-        <v>1129.0725</v>
-      </c>
-      <c r="B3" t="s">
-        <v>9</v>
+        <v>1146.2275000000002</v>
+      </c>
+      <c r="B3">
+        <v>115.41000000000008</v>
       </c>
       <c r="C3" t="s">
-        <v>11</v>
-      </c>
-      <c r="D3">
-        <v>11</v>
+        <v>13</v>
+      </c>
+      <c r="D3" t="s">
+        <v>14</v>
       </c>
       <c r="E3">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="F3">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="G3">
         <v>3</v>
       </c>
-      <c r="I3" t="s">
-        <v>12</v>
+      <c r="H3">
+        <v>2</v>
       </c>
       <c r="J3" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="K3" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="L3" t="s">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="M3" t="s">
         <v>5</v>
@@ -736,157 +745,169 @@
       <c r="N3" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A4">
-        <v>1119.54</v>
-      </c>
-      <c r="B4" t="s">
-        <v>15</v>
+        <v>1128.3224999999998</v>
+      </c>
+      <c r="B4">
+        <v>4.0999999999999091</v>
       </c>
       <c r="C4" t="s">
-        <v>16</v>
-      </c>
-      <c r="D4">
+        <v>18</v>
+      </c>
+      <c r="D4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E4">
         <v>11</v>
       </c>
-      <c r="E4">
-        <v>7</v>
-      </c>
       <c r="F4">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="G4">
         <v>2</v>
       </c>
-      <c r="I4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J4">
-        <v>0</v>
+      <c r="H4">
+        <v>3</v>
+      </c>
+      <c r="J4" t="s">
+        <v>20</v>
       </c>
       <c r="K4">
-        <v>0</v>
+        <v>-18.990000000000002</v>
       </c>
       <c r="L4">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="M4">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="N4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+      <c r="O4">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A5">
-        <v>1092.395</v>
-      </c>
-      <c r="B5" t="s">
-        <v>18</v>
+        <v>1091.6175000000001</v>
+      </c>
+      <c r="B5">
+        <v>42.660000000000082</v>
       </c>
       <c r="C5" t="s">
-        <v>19</v>
-      </c>
-      <c r="D5">
+        <v>21</v>
+      </c>
+      <c r="D5" t="s">
+        <v>22</v>
+      </c>
+      <c r="E5">
         <v>7</v>
       </c>
-      <c r="E5">
+      <c r="F5">
         <v>5</v>
       </c>
-      <c r="F5">
-        <v>1</v>
-      </c>
       <c r="G5">
         <v>1</v>
       </c>
-      <c r="I5" t="s">
-        <v>20</v>
-      </c>
-      <c r="J5">
-        <v>14.25</v>
+      <c r="H5">
+        <v>1</v>
+      </c>
+      <c r="J5" t="s">
+        <v>23</v>
       </c>
       <c r="K5">
-        <v>1</v>
+        <v>24.36</v>
       </c>
       <c r="L5">
         <v>1</v>
       </c>
       <c r="M5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N5">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A6">
-        <v>1090.82</v>
-      </c>
-      <c r="B6" t="s">
-        <v>21</v>
+        <v>1090.7725000000003</v>
+      </c>
+      <c r="B6">
+        <v>51.160000000000082</v>
       </c>
       <c r="C6" t="s">
-        <v>22</v>
-      </c>
-      <c r="D6">
+        <v>24</v>
+      </c>
+      <c r="D6" t="s">
+        <v>25</v>
+      </c>
+      <c r="E6">
         <v>8</v>
       </c>
-      <c r="E6">
+      <c r="F6">
         <v>6</v>
       </c>
-      <c r="F6">
-        <v>0</v>
-      </c>
       <c r="G6">
+        <v>0</v>
+      </c>
+      <c r="H6">
         <v>2</v>
       </c>
-      <c r="I6" t="s">
-        <v>23</v>
-      </c>
-      <c r="J6">
-        <v>-9.8199999999999985</v>
+      <c r="J6" t="s">
+        <v>26</v>
       </c>
       <c r="K6">
-        <v>10</v>
+        <v>-65.31</v>
       </c>
       <c r="L6">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="M6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N6">
         <v>3</v>
       </c>
-    </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O6">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A7">
-        <v>1084.4150000000002</v>
-      </c>
-      <c r="B7" t="s">
-        <v>24</v>
+        <v>1083.2649999999999</v>
+      </c>
+      <c r="B7">
+        <v>39.099999999999909</v>
       </c>
       <c r="C7" t="s">
-        <v>25</v>
-      </c>
-      <c r="D7">
+        <v>27</v>
+      </c>
+      <c r="D7" t="s">
+        <v>28</v>
+      </c>
+      <c r="E7">
         <v>5</v>
-      </c>
-      <c r="E7">
-        <v>2</v>
       </c>
       <c r="F7">
         <v>2</v>
       </c>
       <c r="G7">
-        <v>1</v>
-      </c>
-      <c r="I7" t="s">
-        <v>26</v>
-      </c>
-      <c r="J7">
-        <v>0</v>
+        <v>2</v>
+      </c>
+      <c r="H7">
+        <v>1</v>
+      </c>
+      <c r="J7" t="s">
+        <v>29</v>
       </c>
       <c r="K7">
         <v>0</v>
@@ -900,529 +921,598 @@
       <c r="N7">
         <v>0</v>
       </c>
-    </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A8">
-        <v>1056.81125</v>
-      </c>
-      <c r="B8" t="s">
-        <v>27</v>
+        <v>1035.8690000000001</v>
+      </c>
+      <c r="B8">
+        <v>-4.6500000000000909</v>
       </c>
       <c r="C8" t="s">
-        <v>28</v>
-      </c>
-      <c r="D8">
-        <v>18</v>
+        <v>30</v>
+      </c>
+      <c r="D8" t="s">
+        <v>31</v>
       </c>
       <c r="E8">
+        <v>22</v>
+      </c>
+      <c r="F8">
+        <v>12</v>
+      </c>
+      <c r="G8">
+        <v>5</v>
+      </c>
+      <c r="H8">
+        <v>5</v>
+      </c>
+      <c r="J8" t="s">
+        <v>32</v>
+      </c>
+      <c r="K8">
+        <v>-59.940000000000005</v>
+      </c>
+      <c r="L8">
+        <v>31</v>
+      </c>
+      <c r="M8">
+        <v>7</v>
+      </c>
+      <c r="N8">
+        <v>4</v>
+      </c>
+      <c r="O8">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A9">
+        <v>1027.4275</v>
+      </c>
+      <c r="B9">
+        <v>-26.789999999999964</v>
+      </c>
+      <c r="C9" t="s">
+        <v>33</v>
+      </c>
+      <c r="D9" t="s">
+        <v>34</v>
+      </c>
+      <c r="E9">
+        <v>2</v>
+      </c>
+      <c r="F9">
+        <v>0</v>
+      </c>
+      <c r="G9">
+        <v>0</v>
+      </c>
+      <c r="H9">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A10">
+        <v>1018.7049999999998</v>
+      </c>
+      <c r="B10">
+        <v>-18.600000000000023</v>
+      </c>
+      <c r="C10" t="s">
+        <v>35</v>
+      </c>
+      <c r="D10" t="s">
+        <v>36</v>
+      </c>
+      <c r="E10">
+        <v>9</v>
+      </c>
+      <c r="F10">
+        <v>4</v>
+      </c>
+      <c r="G10">
+        <v>0</v>
+      </c>
+      <c r="H10">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A11">
+        <v>1001.8340000000001</v>
+      </c>
+      <c r="B11">
+        <v>0</v>
+      </c>
+      <c r="C11" t="s">
+        <v>37</v>
+      </c>
+      <c r="D11" t="s">
+        <v>38</v>
+      </c>
+      <c r="E11">
+        <v>0</v>
+      </c>
+      <c r="F11">
+        <v>0</v>
+      </c>
+      <c r="G11">
+        <v>0</v>
+      </c>
+      <c r="H11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A12">
+        <v>1000.7408636363637</v>
+      </c>
+      <c r="B12">
+        <v>69.860000000000014</v>
+      </c>
+      <c r="C12" t="s">
+        <v>39</v>
+      </c>
+      <c r="D12" t="s">
+        <v>40</v>
+      </c>
+      <c r="E12">
+        <v>19</v>
+      </c>
+      <c r="F12">
+        <v>14</v>
+      </c>
+      <c r="G12">
+        <v>1</v>
+      </c>
+      <c r="H12">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A13">
+        <v>1000.0350000000001</v>
+      </c>
+      <c r="B13">
+        <v>7.4500000000000455</v>
+      </c>
+      <c r="C13" t="s">
+        <v>41</v>
+      </c>
+      <c r="D13" t="s">
+        <v>42</v>
+      </c>
+      <c r="E13">
         <v>10</v>
       </c>
-      <c r="F8">
+      <c r="F13">
         <v>5</v>
       </c>
-      <c r="G8">
+      <c r="G13">
+        <v>2</v>
+      </c>
+      <c r="H13">
         <v>3</v>
       </c>
-      <c r="I8" t="s">
-        <v>29</v>
-      </c>
-      <c r="J8">
-        <v>4.4300000000000015</v>
-      </c>
-      <c r="K8">
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A14">
+        <v>995.99900000000014</v>
+      </c>
+      <c r="B14">
+        <v>-30.870000000000005</v>
+      </c>
+      <c r="C14" t="s">
+        <v>43</v>
+      </c>
+      <c r="D14" t="s">
+        <v>44</v>
+      </c>
+      <c r="E14">
+        <v>10</v>
+      </c>
+      <c r="F14">
+        <v>4</v>
+      </c>
+      <c r="G14">
+        <v>1</v>
+      </c>
+      <c r="H14">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A15">
+        <v>974.45086363636369</v>
+      </c>
+      <c r="B15">
+        <v>43.57000000000005</v>
+      </c>
+      <c r="C15" t="s">
+        <v>45</v>
+      </c>
+      <c r="D15" t="s">
+        <v>46</v>
+      </c>
+      <c r="E15">
+        <v>16</v>
+      </c>
+      <c r="F15">
+        <v>6</v>
+      </c>
+      <c r="G15">
+        <v>3</v>
+      </c>
+      <c r="H15">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A16">
+        <v>966.74</v>
+      </c>
+      <c r="B16">
+        <v>-40.360000000000014</v>
+      </c>
+      <c r="C16" t="s">
+        <v>47</v>
+      </c>
+      <c r="D16" t="s">
+        <v>48</v>
+      </c>
+      <c r="E16">
+        <v>3</v>
+      </c>
+      <c r="F16">
+        <v>0</v>
+      </c>
+      <c r="G16">
+        <v>0</v>
+      </c>
+      <c r="H16">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A17">
+        <v>965.73086363636367</v>
+      </c>
+      <c r="B17">
+        <v>34.850000000000023</v>
+      </c>
+      <c r="C17" t="s">
+        <v>49</v>
+      </c>
+      <c r="D17" t="s">
+        <v>50</v>
+      </c>
+      <c r="E17">
+        <v>15</v>
+      </c>
+      <c r="F17">
+        <v>9</v>
+      </c>
+      <c r="G17">
+        <v>1</v>
+      </c>
+      <c r="H17">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A18">
+        <v>957.64086363636363</v>
+      </c>
+      <c r="B18">
+        <v>26.759999999999991</v>
+      </c>
+      <c r="C18" t="s">
+        <v>51</v>
+      </c>
+      <c r="D18" t="s">
+        <v>52</v>
+      </c>
+      <c r="E18">
+        <v>21</v>
+      </c>
+      <c r="F18">
+        <v>12</v>
+      </c>
+      <c r="G18">
+        <v>1</v>
+      </c>
+      <c r="H18">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A19">
+        <v>948.87</v>
+      </c>
+      <c r="B19">
+        <v>-21.149999999999977</v>
+      </c>
+      <c r="C19" t="s">
+        <v>53</v>
+      </c>
+      <c r="D19" t="s">
+        <v>54</v>
+      </c>
+      <c r="E19">
+        <v>5</v>
+      </c>
+      <c r="F19">
+        <v>2</v>
+      </c>
+      <c r="G19">
+        <v>0</v>
+      </c>
+      <c r="H19">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A20">
+        <v>941.88086363636364</v>
+      </c>
+      <c r="B20">
         <v>11</v>
       </c>
-      <c r="L8">
+      <c r="C20" t="s">
+        <v>55</v>
+      </c>
+      <c r="D20" t="s">
+        <v>56</v>
+      </c>
+      <c r="E20">
+        <v>17</v>
+      </c>
+      <c r="F20">
+        <v>5</v>
+      </c>
+      <c r="G20">
+        <v>3</v>
+      </c>
+      <c r="H20">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A21">
+        <v>929.84086363636368</v>
+      </c>
+      <c r="B21">
+        <v>-1.0399999999999636</v>
+      </c>
+      <c r="C21" t="s">
+        <v>57</v>
+      </c>
+      <c r="D21" t="s">
+        <v>58</v>
+      </c>
+      <c r="E21">
+        <v>2</v>
+      </c>
+      <c r="F21">
+        <v>1</v>
+      </c>
+      <c r="G21">
+        <v>0</v>
+      </c>
+      <c r="H21">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A22">
+        <v>929.4308636363636</v>
+      </c>
+      <c r="B22">
+        <v>-1.4500000000000455</v>
+      </c>
+      <c r="C22" t="s">
+        <v>59</v>
+      </c>
+      <c r="D22" t="s">
+        <v>60</v>
+      </c>
+      <c r="E22">
+        <v>2</v>
+      </c>
+      <c r="F22">
+        <v>0</v>
+      </c>
+      <c r="G22">
+        <v>1</v>
+      </c>
+      <c r="H22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A23">
+        <v>928.27086363636363</v>
+      </c>
+      <c r="B23">
+        <v>-2.6100000000000136</v>
+      </c>
+      <c r="C23" t="s">
+        <v>61</v>
+      </c>
+      <c r="D23" t="s">
+        <v>62</v>
+      </c>
+      <c r="E23">
+        <v>11</v>
+      </c>
+      <c r="F23">
+        <v>3</v>
+      </c>
+      <c r="G23">
+        <v>0</v>
+      </c>
+      <c r="H23">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A24">
+        <v>923.04900000000009</v>
+      </c>
+      <c r="B24">
+        <v>-28.659999999999968</v>
+      </c>
+      <c r="C24" t="s">
+        <v>63</v>
+      </c>
+      <c r="D24" t="s">
+        <v>64</v>
+      </c>
+      <c r="E24">
+        <v>10</v>
+      </c>
+      <c r="F24">
+        <v>4</v>
+      </c>
+      <c r="G24">
+        <v>2</v>
+      </c>
+      <c r="H24">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A25">
+        <v>919.69086363636359</v>
+      </c>
+      <c r="B25">
+        <v>-11.190000000000055</v>
+      </c>
+      <c r="C25" t="s">
+        <v>65</v>
+      </c>
+      <c r="D25" t="s">
+        <v>66</v>
+      </c>
+      <c r="E25">
         <v>6</v>
       </c>
-      <c r="M8">
-        <v>2</v>
-      </c>
-      <c r="N8">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A9">
-        <v>1028.7775000000001</v>
-      </c>
-      <c r="B9" t="s">
-        <v>30</v>
-      </c>
-      <c r="C9" t="s">
-        <v>31</v>
-      </c>
-      <c r="D9">
-        <v>2</v>
-      </c>
-      <c r="E9">
-        <v>0</v>
-      </c>
-      <c r="F9">
-        <v>0</v>
-      </c>
-      <c r="G9">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A10">
-        <v>1019.7900000000001</v>
-      </c>
-      <c r="B10" t="s">
-        <v>32</v>
-      </c>
-      <c r="C10" t="s">
-        <v>33</v>
-      </c>
-      <c r="D10">
-        <v>9</v>
-      </c>
-      <c r="E10">
+      <c r="F25">
+        <v>1</v>
+      </c>
+      <c r="G25">
+        <v>1</v>
+      </c>
+      <c r="H25">
         <v>4</v>
       </c>
-      <c r="F10">
-        <v>0</v>
-      </c>
-      <c r="G10">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A11">
-        <v>1006.7609090909091</v>
-      </c>
-      <c r="B11" t="s">
-        <v>34</v>
-      </c>
-      <c r="C11" t="s">
-        <v>35</v>
-      </c>
-      <c r="D11">
-        <v>17</v>
-      </c>
-      <c r="E11">
-        <v>12</v>
-      </c>
-      <c r="F11">
-        <v>1</v>
-      </c>
-      <c r="G11">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A12">
-        <v>1006.55</v>
-      </c>
-      <c r="B12" t="s">
-        <v>36</v>
-      </c>
-      <c r="C12" t="s">
-        <v>37</v>
-      </c>
-      <c r="D12">
-        <v>10</v>
-      </c>
-      <c r="E12">
-        <v>5</v>
-      </c>
-      <c r="F12">
-        <v>2</v>
-      </c>
-      <c r="G12">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A13">
-        <v>1001.55125</v>
-      </c>
-      <c r="B13" t="s">
-        <v>38</v>
-      </c>
-      <c r="C13" t="s">
-        <v>39</v>
-      </c>
-      <c r="D13">
-        <v>0</v>
-      </c>
-      <c r="E13">
-        <v>0</v>
-      </c>
-      <c r="F13">
-        <v>0</v>
-      </c>
-      <c r="G13">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A14">
-        <v>998.44125000000008</v>
-      </c>
-      <c r="B14" t="s">
-        <v>40</v>
-      </c>
-      <c r="C14" t="s">
-        <v>41</v>
-      </c>
-      <c r="D14">
-        <v>10</v>
-      </c>
-      <c r="E14">
-        <v>4</v>
-      </c>
-      <c r="F14">
-        <v>1</v>
-      </c>
-      <c r="G14">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A15">
-        <v>976.28090909090906</v>
-      </c>
-      <c r="B15" t="s">
-        <v>42</v>
-      </c>
-      <c r="C15" t="s">
-        <v>43</v>
-      </c>
-      <c r="D15">
-        <v>19</v>
-      </c>
-      <c r="E15">
-        <v>12</v>
-      </c>
-      <c r="F15">
-        <v>1</v>
-      </c>
-      <c r="G15">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A16">
-        <v>973.00090909090909</v>
-      </c>
-      <c r="B16" t="s">
-        <v>44</v>
-      </c>
-      <c r="C16" t="s">
-        <v>45</v>
-      </c>
-      <c r="D16">
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A26">
+        <v>911.94749999999999</v>
+      </c>
+      <c r="B26">
+        <v>-69.710000000000036</v>
+      </c>
+      <c r="C26" t="s">
+        <v>67</v>
+      </c>
+      <c r="D26" t="s">
+        <v>68</v>
+      </c>
+      <c r="E26">
         <v>15</v>
-      </c>
-      <c r="E16">
-        <v>9</v>
-      </c>
-      <c r="F16">
-        <v>1</v>
-      </c>
-      <c r="G16">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A17">
-        <v>967.49750000000006</v>
-      </c>
-      <c r="B17" t="s">
-        <v>46</v>
-      </c>
-      <c r="C17" t="s">
-        <v>47</v>
-      </c>
-      <c r="D17">
-        <v>3</v>
-      </c>
-      <c r="E17">
-        <v>0</v>
-      </c>
-      <c r="F17">
-        <v>0</v>
-      </c>
-      <c r="G17">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A18">
-        <v>955.31090909090904</v>
-      </c>
-      <c r="B18" t="s">
-        <v>48</v>
-      </c>
-      <c r="C18" t="s">
-        <v>49</v>
-      </c>
-      <c r="D18">
-        <v>12</v>
-      </c>
-      <c r="E18">
-        <v>4</v>
-      </c>
-      <c r="F18">
-        <v>2</v>
-      </c>
-      <c r="G18">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A19">
-        <v>951.13250000000005</v>
-      </c>
-      <c r="B19" t="s">
-        <v>50</v>
-      </c>
-      <c r="C19" t="s">
-        <v>51</v>
-      </c>
-      <c r="D19">
-        <v>5</v>
-      </c>
-      <c r="E19">
-        <v>2</v>
-      </c>
-      <c r="F19">
-        <v>0</v>
-      </c>
-      <c r="G19">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A20">
-        <v>948.55090909090904</v>
-      </c>
-      <c r="B20" t="s">
-        <v>52</v>
-      </c>
-      <c r="C20" t="s">
-        <v>53</v>
-      </c>
-      <c r="D20">
-        <v>15</v>
-      </c>
-      <c r="E20">
-        <v>5</v>
-      </c>
-      <c r="F20">
-        <v>3</v>
-      </c>
-      <c r="G20">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A21">
-        <v>935.80090909090904</v>
-      </c>
-      <c r="B21" t="s">
-        <v>54</v>
-      </c>
-      <c r="C21" t="s">
-        <v>55</v>
-      </c>
-      <c r="D21">
-        <v>0</v>
-      </c>
-      <c r="E21">
-        <v>0</v>
-      </c>
-      <c r="F21">
-        <v>0</v>
-      </c>
-      <c r="G21">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A22">
-        <v>933.23090909090899</v>
-      </c>
-      <c r="B22" t="s">
-        <v>56</v>
-      </c>
-      <c r="C22" t="s">
-        <v>57</v>
-      </c>
-      <c r="D22">
-        <v>2</v>
-      </c>
-      <c r="E22">
-        <v>0</v>
-      </c>
-      <c r="F22">
-        <v>1</v>
-      </c>
-      <c r="G22">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A23">
-        <v>928.66125000000011</v>
-      </c>
-      <c r="B23" t="s">
-        <v>58</v>
-      </c>
-      <c r="C23" t="s">
-        <v>59</v>
-      </c>
-      <c r="D23">
-        <v>8</v>
-      </c>
-      <c r="E23">
-        <v>3</v>
-      </c>
-      <c r="F23">
-        <v>1</v>
-      </c>
-      <c r="G23">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A24">
-        <v>926.50090909090909</v>
-      </c>
-      <c r="B24" t="s">
-        <v>60</v>
-      </c>
-      <c r="C24" t="s">
-        <v>61</v>
-      </c>
-      <c r="D24">
-        <v>11</v>
-      </c>
-      <c r="E24">
-        <v>3</v>
-      </c>
-      <c r="F24">
-        <v>0</v>
-      </c>
-      <c r="G24">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A25">
-        <v>918.03090909090906</v>
-      </c>
-      <c r="B25" t="s">
-        <v>62</v>
-      </c>
-      <c r="C25" t="s">
-        <v>63</v>
-      </c>
-      <c r="D25">
-        <v>6</v>
-      </c>
-      <c r="E25">
-        <v>1</v>
-      </c>
-      <c r="F25">
-        <v>1</v>
-      </c>
-      <c r="G25">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A26">
-        <v>913.26249999999993</v>
-      </c>
-      <c r="B26" t="s">
-        <v>64</v>
-      </c>
-      <c r="C26" t="s">
-        <v>65</v>
-      </c>
-      <c r="D26">
-        <v>15</v>
-      </c>
-      <c r="E26">
-        <v>3</v>
       </c>
       <c r="F26">
         <v>3</v>
       </c>
       <c r="G26">
+        <v>3</v>
+      </c>
+      <c r="H26">
         <v>9</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A27">
-        <v>906.470909090909</v>
-      </c>
-      <c r="B27" t="s">
-        <v>66</v>
+        <v>906.11086363636366</v>
+      </c>
+      <c r="B27">
+        <v>-24.769999999999982</v>
       </c>
       <c r="C27" t="s">
-        <v>67</v>
-      </c>
-      <c r="D27">
+        <v>69</v>
+      </c>
+      <c r="D27" t="s">
+        <v>70</v>
+      </c>
+      <c r="E27">
         <v>7</v>
       </c>
-      <c r="E27">
-        <v>1</v>
-      </c>
       <c r="F27">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G27">
+        <v>0</v>
+      </c>
+      <c r="H27">
         <v>6</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A28">
-        <v>902.18124999999998</v>
-      </c>
-      <c r="B28" t="s">
-        <v>68</v>
+        <v>889.4408636363637</v>
+      </c>
+      <c r="B28">
+        <v>-41.439999999999941</v>
       </c>
       <c r="C28" t="s">
-        <v>69</v>
-      </c>
-      <c r="D28">
-        <v>25</v>
+        <v>71</v>
+      </c>
+      <c r="D28" t="s">
+        <v>72</v>
       </c>
       <c r="E28">
+        <v>7</v>
+      </c>
+      <c r="F28">
+        <v>1</v>
+      </c>
+      <c r="G28">
+        <v>0</v>
+      </c>
+      <c r="H28">
         <v>6</v>
       </c>
-      <c r="F28">
-        <v>3</v>
-      </c>
-      <c r="G28">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A29">
-        <v>892.01090909090908</v>
-      </c>
-      <c r="B29" t="s">
-        <v>70</v>
+        <v>874.28399999999999</v>
+      </c>
+      <c r="B29">
+        <v>-59.940000000000055</v>
       </c>
       <c r="C29" t="s">
-        <v>71</v>
-      </c>
-      <c r="D29">
+        <v>10</v>
+      </c>
+      <c r="D29" t="s">
+        <v>12</v>
+      </c>
+      <c r="E29">
+        <v>31</v>
+      </c>
+      <c r="F29">
         <v>7</v>
       </c>
-      <c r="E29">
-        <v>1</v>
-      </c>
-      <c r="F29">
-        <v>0</v>
-      </c>
       <c r="G29">
-        <v>6</v>
+        <v>4</v>
+      </c>
+      <c r="H29">
+        <v>20</v>
       </c>
     </row>
   </sheetData>

--- a/Ranking_Data.xlsx
+++ b/Ranking_Data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="c:\Users\원영이\Desktop\ATL AUTO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C0C1F079-8EC9-4916-93ED-B6334E3F0518}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{281A37ED-857D-4923-978E-4BD17FAD50E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="314" yWindow="955" windowWidth="36185" windowHeight="19576" xr2:uid="{7FD324CC-1F2F-4F87-853F-C9D8FCD7DE16}"/>
+    <workbookView xWindow="-114" yWindow="-114" windowWidth="36727" windowHeight="20317" xr2:uid="{5CAA5E78-16DA-4BC0-9284-6E226C75FF81}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -65,199 +65,199 @@
     <t>패</t>
   </si>
   <si>
+    <t>UNIT</t>
+  </si>
+  <si>
+    <t>AS 로마</t>
+  </si>
+  <si>
+    <t>17시즌</t>
+  </si>
+  <si>
     <t>개포동덕배</t>
   </si>
   <si>
     <t>바이에른 뮌헨</t>
   </si>
   <si>
+    <t>대회종류</t>
+  </si>
+  <si>
+    <t>ELO 변동값</t>
+  </si>
+  <si>
+    <t>경기 수</t>
+  </si>
+  <si>
+    <t>Voor</t>
+  </si>
+  <si>
+    <t>첼시</t>
+  </si>
+  <si>
+    <t>1부리그</t>
+  </si>
+  <si>
+    <t>검정소</t>
+  </si>
+  <si>
+    <t>AC 밀란</t>
+  </si>
+  <si>
+    <t>FA컵</t>
+  </si>
+  <si>
+    <t>Special블루</t>
+  </si>
+  <si>
+    <t>아스널</t>
+  </si>
+  <si>
+    <t>UEFA_A조</t>
+  </si>
+  <si>
+    <t>은안</t>
+  </si>
+  <si>
+    <t>맨체스터 시티</t>
+  </si>
+  <si>
+    <t>UEFA Tournament</t>
+  </si>
+  <si>
+    <t>오스트리아</t>
+  </si>
+  <si>
+    <t>마인츠</t>
+  </si>
+  <si>
+    <t>전체 합계</t>
+  </si>
+  <si>
+    <t>앙쿠</t>
+  </si>
+  <si>
+    <t>아틀레티코 마드리드</t>
+  </si>
+  <si>
+    <t>킹왕두</t>
+  </si>
+  <si>
+    <t>리버풀</t>
+  </si>
+  <si>
+    <t>아들러</t>
+  </si>
+  <si>
+    <t>프랑크푸르트</t>
+  </si>
+  <si>
+    <t>호야국2인</t>
+  </si>
+  <si>
+    <t>SSC 나폴리</t>
+  </si>
+  <si>
+    <t>ZD장인지참치</t>
+  </si>
+  <si>
+    <t>레버쿠젠</t>
+  </si>
+  <si>
+    <t>방덕</t>
+  </si>
+  <si>
+    <t>인테르</t>
+  </si>
+  <si>
+    <t>비주류중독</t>
+  </si>
+  <si>
+    <t>셀틱 FC</t>
+  </si>
+  <si>
+    <t>콩콩콩룔</t>
+  </si>
+  <si>
+    <t>라치오</t>
+  </si>
+  <si>
+    <t>여수가스</t>
+  </si>
+  <si>
+    <t>AS 모나코</t>
+  </si>
+  <si>
+    <t>suma수마</t>
+  </si>
+  <si>
+    <t>ACF 피오렌티나</t>
+  </si>
+  <si>
+    <t>Gucci와퍼</t>
+  </si>
+  <si>
+    <t>함부르크SV</t>
+  </si>
+  <si>
+    <t>경남FC가즈아</t>
+  </si>
+  <si>
+    <t>경남 FC</t>
+  </si>
+  <si>
+    <t>스페인전도사</t>
+  </si>
+  <si>
+    <t>RC 셀타 비고</t>
+  </si>
+  <si>
+    <t>셀래스틴</t>
+  </si>
+  <si>
+    <t>바르셀로나</t>
+  </si>
+  <si>
+    <t>0708ManUtd</t>
+  </si>
+  <si>
+    <t>레알 마드리드</t>
+  </si>
+  <si>
+    <t>용신</t>
+  </si>
+  <si>
+    <t>토트넘</t>
+  </si>
+  <si>
+    <t>Gucci차붐</t>
+  </si>
+  <si>
+    <t>전북 현대 모터스</t>
+  </si>
+  <si>
+    <t>ShangHaiPortFC</t>
+  </si>
+  <si>
+    <t>상하이 선화</t>
+  </si>
+  <si>
+    <t>A지냐크</t>
+  </si>
+  <si>
+    <t>올랭피크 마르세유</t>
+  </si>
+  <si>
+    <t>겐지간지</t>
+  </si>
+  <si>
+    <t>파리 생제르맹</t>
+  </si>
+  <si>
     <t>Legend독수리</t>
   </si>
   <si>
-    <t>17시즌</t>
-  </si>
-  <si>
     <t>맨체스터 유나이티드</t>
-  </si>
-  <si>
-    <t>UNIT</t>
-  </si>
-  <si>
-    <t>AS 로마</t>
-  </si>
-  <si>
-    <t>대회종류</t>
-  </si>
-  <si>
-    <t>ELO 변동값</t>
-  </si>
-  <si>
-    <t>경기 수</t>
-  </si>
-  <si>
-    <t>Voor</t>
-  </si>
-  <si>
-    <t>첼시</t>
-  </si>
-  <si>
-    <t>3부리그</t>
-  </si>
-  <si>
-    <t>검정소</t>
-  </si>
-  <si>
-    <t>AC 밀란</t>
-  </si>
-  <si>
-    <t>FA컵</t>
-  </si>
-  <si>
-    <t>Special블루</t>
-  </si>
-  <si>
-    <t>아스널</t>
-  </si>
-  <si>
-    <t>UEFA_A조</t>
-  </si>
-  <si>
-    <t>은안</t>
-  </si>
-  <si>
-    <t>맨체스터 시티</t>
-  </si>
-  <si>
-    <t>UEFA Tournament</t>
-  </si>
-  <si>
-    <t>오스트리아</t>
-  </si>
-  <si>
-    <t>마인츠</t>
-  </si>
-  <si>
-    <t>전체 합계</t>
-  </si>
-  <si>
-    <t>킹왕두</t>
-  </si>
-  <si>
-    <t>리버풀</t>
-  </si>
-  <si>
-    <t>아들러</t>
-  </si>
-  <si>
-    <t>프랑크푸르트</t>
-  </si>
-  <si>
-    <t>호야국2인</t>
-  </si>
-  <si>
-    <t>SSC 나폴리</t>
-  </si>
-  <si>
-    <t>ZD장인지참치</t>
-  </si>
-  <si>
-    <t>레버쿠젠</t>
-  </si>
-  <si>
-    <t>앙쿠</t>
-  </si>
-  <si>
-    <t>아틀레티코 마드리드</t>
-  </si>
-  <si>
-    <t>방덕</t>
-  </si>
-  <si>
-    <t>인테르</t>
-  </si>
-  <si>
-    <t>비주류중독</t>
-  </si>
-  <si>
-    <t>셀틱 FC</t>
-  </si>
-  <si>
-    <t>콩콩콩룔</t>
-  </si>
-  <si>
-    <t>라치오</t>
-  </si>
-  <si>
-    <t>여수가스</t>
-  </si>
-  <si>
-    <t>AS 모나코</t>
-  </si>
-  <si>
-    <t>suma수마</t>
-  </si>
-  <si>
-    <t>ACF 피오렌티나</t>
-  </si>
-  <si>
-    <t>Gucci와퍼</t>
-  </si>
-  <si>
-    <t>함부르크SV</t>
-  </si>
-  <si>
-    <t>스페인전도사</t>
-  </si>
-  <si>
-    <t>RC 셀타 비고</t>
-  </si>
-  <si>
-    <t>셀래스틴</t>
-  </si>
-  <si>
-    <t>바르셀로나</t>
-  </si>
-  <si>
-    <t>0708ManUtd</t>
-  </si>
-  <si>
-    <t>레알 마드리드</t>
-  </si>
-  <si>
-    <t>용신</t>
-  </si>
-  <si>
-    <t>토트넘</t>
-  </si>
-  <si>
-    <t>경남FC가즈아</t>
-  </si>
-  <si>
-    <t>경남 FC</t>
-  </si>
-  <si>
-    <t>A지냐크</t>
-  </si>
-  <si>
-    <t>올랭피크 마르세유</t>
-  </si>
-  <si>
-    <t>Gucci차붐</t>
-  </si>
-  <si>
-    <t>전북 현대 모터스</t>
-  </si>
-  <si>
-    <t>ShangHaiPortFC</t>
-  </si>
-  <si>
-    <t>상하이 선화</t>
-  </si>
-  <si>
-    <t>겐지간지</t>
-  </si>
-  <si>
-    <t>파리 생제르맹</t>
   </si>
 </sst>
 </file>
@@ -640,7 +640,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{59BFAA15-8B7E-443F-9A3D-B8662BDD0CB7}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F7010920-4F4D-4D1C-B896-09D027111F1B}">
   <dimension ref="A1:O29"/>
   <sheetFormatPr defaultRowHeight="15.7" x14ac:dyDescent="0.3"/>
   <sheetData>
@@ -672,10 +672,10 @@
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A2">
-        <v>1153.174</v>
+        <v>1155.4175</v>
       </c>
       <c r="B2">
-        <v>38.309999999999945</v>
+        <v>124.59999999999991</v>
       </c>
       <c r="C2" t="s">
         <v>8</v>
@@ -684,60 +684,60 @@
         <v>9</v>
       </c>
       <c r="E2">
+        <v>19</v>
+      </c>
+      <c r="F2">
+        <v>12</v>
+      </c>
+      <c r="G2">
         <v>4</v>
       </c>
-      <c r="F2">
-        <v>4</v>
-      </c>
-      <c r="G2">
-        <v>0</v>
-      </c>
       <c r="H2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J2" t="s">
+        <v>8</v>
+      </c>
+      <c r="L2" t="s">
         <v>10</v>
       </c>
-      <c r="L2" t="s">
-        <v>11</v>
-      </c>
       <c r="M2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A3">
-        <v>1146.2275000000002</v>
+        <v>1153.174</v>
       </c>
       <c r="B3">
-        <v>115.41000000000008</v>
+        <v>38.309999999999945</v>
       </c>
       <c r="C3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E3">
+        <v>4</v>
+      </c>
+      <c r="F3">
+        <v>4</v>
+      </c>
+      <c r="G3">
+        <v>0</v>
+      </c>
+      <c r="H3">
+        <v>0</v>
+      </c>
+      <c r="J3" t="s">
         <v>13</v>
       </c>
-      <c r="D3" t="s">
+      <c r="K3" t="s">
         <v>14</v>
       </c>
-      <c r="E3">
+      <c r="L3" t="s">
         <v>15</v>
-      </c>
-      <c r="F3">
-        <v>10</v>
-      </c>
-      <c r="G3">
-        <v>3</v>
-      </c>
-      <c r="H3">
-        <v>2</v>
-      </c>
-      <c r="J3" t="s">
-        <v>15</v>
-      </c>
-      <c r="K3" t="s">
-        <v>16</v>
-      </c>
-      <c r="L3" t="s">
-        <v>17</v>
       </c>
       <c r="M3" t="s">
         <v>5</v>
@@ -757,10 +757,10 @@
         <v>4.0999999999999091</v>
       </c>
       <c r="C4" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D4" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E4">
         <v>11</v>
@@ -775,54 +775,54 @@
         <v>3</v>
       </c>
       <c r="J4" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="K4">
-        <v>-18.990000000000002</v>
+        <v>67.53</v>
       </c>
       <c r="L4">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="M4">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="N4">
+        <v>2</v>
+      </c>
+      <c r="O4">
         <v>1</v>
-      </c>
-      <c r="O4">
-        <v>12</v>
       </c>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A5">
-        <v>1091.6175000000001</v>
+        <v>1093.6675</v>
       </c>
       <c r="B5">
-        <v>42.660000000000082</v>
+        <v>44.710000000000036</v>
       </c>
       <c r="C5" t="s">
+        <v>19</v>
+      </c>
+      <c r="D5" t="s">
+        <v>20</v>
+      </c>
+      <c r="E5">
+        <v>11</v>
+      </c>
+      <c r="F5">
+        <v>6</v>
+      </c>
+      <c r="G5">
+        <v>2</v>
+      </c>
+      <c r="H5">
+        <v>3</v>
+      </c>
+      <c r="J5" t="s">
         <v>21</v>
       </c>
-      <c r="D5" t="s">
-        <v>22</v>
-      </c>
-      <c r="E5">
-        <v>7</v>
-      </c>
-      <c r="F5">
-        <v>5</v>
-      </c>
-      <c r="G5">
-        <v>1</v>
-      </c>
-      <c r="H5">
-        <v>1</v>
-      </c>
-      <c r="J5" t="s">
-        <v>23</v>
-      </c>
       <c r="K5">
-        <v>24.36</v>
+        <v>19.260000000000002</v>
       </c>
       <c r="L5">
         <v>1</v>
@@ -845,10 +845,10 @@
         <v>51.160000000000082</v>
       </c>
       <c r="C6" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D6" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="E6">
         <v>8</v>
@@ -863,22 +863,22 @@
         <v>2</v>
       </c>
       <c r="J6" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="K6">
-        <v>-65.31</v>
+        <v>37.81</v>
       </c>
       <c r="L6">
         <v>12</v>
       </c>
       <c r="M6">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="N6">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O6">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.3">
@@ -889,10 +889,10 @@
         <v>39.099999999999909</v>
       </c>
       <c r="C7" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D7" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E7">
         <v>5</v>
@@ -907,7 +907,7 @@
         <v>1</v>
       </c>
       <c r="J7" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="K7">
         <v>0</v>
@@ -927,176 +927,176 @@
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A8">
-        <v>1035.8690000000001</v>
+        <v>1035.0690000000002</v>
       </c>
       <c r="B8">
-        <v>-4.6500000000000909</v>
+        <v>-5.4500000000000455</v>
       </c>
       <c r="C8" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D8" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="E8">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="F8">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G8">
         <v>5</v>
       </c>
       <c r="H8">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J8" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="K8">
-        <v>-59.940000000000005</v>
+        <v>124.60000000000001</v>
       </c>
       <c r="L8">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="M8">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="N8">
         <v>4</v>
       </c>
       <c r="O8">
-        <v>20</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A9">
-        <v>1027.4275</v>
+        <v>1029.7650000000001</v>
       </c>
       <c r="B9">
-        <v>-26.789999999999964</v>
+        <v>37.180000000000064</v>
       </c>
       <c r="C9" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="D9" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="E9">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="F9">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="G9">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H9">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A10">
-        <v>1018.7049999999998</v>
+        <v>1027.5374999999999</v>
       </c>
       <c r="B10">
-        <v>-18.600000000000023</v>
+        <v>-26.680000000000064</v>
       </c>
       <c r="C10" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D10" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E10">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="F10">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G10">
         <v>0</v>
       </c>
       <c r="H10">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A11">
-        <v>1001.8340000000001</v>
+        <v>1018.7049999999998</v>
       </c>
       <c r="B11">
-        <v>0</v>
+        <v>-18.600000000000023</v>
       </c>
       <c r="C11" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D11" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E11">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="F11">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G11">
         <v>0</v>
       </c>
       <c r="H11">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A12">
-        <v>1000.7408636363637</v>
+        <v>1001.8340000000001</v>
       </c>
       <c r="B12">
-        <v>69.860000000000014</v>
+        <v>0</v>
       </c>
       <c r="C12" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D12" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E12">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="F12">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="G12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H12">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A13">
-        <v>1000.0350000000001</v>
+        <v>998.58086363636369</v>
       </c>
       <c r="B13">
-        <v>7.4500000000000455</v>
+        <v>67.700000000000045</v>
       </c>
       <c r="C13" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D13" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E13">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="F13">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="G13">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H13">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.3">
@@ -1107,10 +1107,10 @@
         <v>-30.870000000000005</v>
       </c>
       <c r="C14" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D14" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="E14">
         <v>10</v>
@@ -1127,16 +1127,16 @@
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A15">
-        <v>974.45086363636369</v>
+        <v>974.53086363636362</v>
       </c>
       <c r="B15">
-        <v>43.57000000000005</v>
+        <v>43.649999999999977</v>
       </c>
       <c r="C15" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="D15" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="E15">
         <v>16</v>
@@ -1159,10 +1159,10 @@
         <v>-40.360000000000014</v>
       </c>
       <c r="C16" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D16" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E16">
         <v>3</v>
@@ -1185,10 +1185,10 @@
         <v>34.850000000000023</v>
       </c>
       <c r="C17" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D17" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="E17">
         <v>15</v>
@@ -1205,28 +1205,28 @@
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A18">
-        <v>957.64086363636363</v>
+        <v>953.15086363636362</v>
       </c>
       <c r="B18">
-        <v>26.759999999999991</v>
+        <v>22.269999999999982</v>
       </c>
       <c r="C18" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D18" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E18">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="F18">
         <v>12</v>
       </c>
       <c r="G18">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H18">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.3">
@@ -1237,10 +1237,10 @@
         <v>-21.149999999999977</v>
       </c>
       <c r="C19" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D19" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="E19">
         <v>5</v>
@@ -1257,210 +1257,210 @@
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A20">
-        <v>941.88086363636364</v>
+        <v>941.61900000000003</v>
       </c>
       <c r="B20">
-        <v>11</v>
+        <v>-10.090000000000032</v>
       </c>
       <c r="C20" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D20" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E20">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="F20">
+        <v>6</v>
+      </c>
+      <c r="G20">
+        <v>2</v>
+      </c>
+      <c r="H20">
         <v>5</v>
-      </c>
-      <c r="G20">
-        <v>3</v>
-      </c>
-      <c r="H20">
-        <v>9</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A21">
-        <v>929.84086363636368</v>
+        <v>941.3208636363637</v>
       </c>
       <c r="B21">
-        <v>-1.0399999999999636</v>
+        <v>10.440000000000055</v>
       </c>
       <c r="C21" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D21" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="E21">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="F21">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G21">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H21">
-        <v>1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A22">
-        <v>929.4308636363636</v>
+        <v>938.33086363636369</v>
       </c>
       <c r="B22">
-        <v>-1.4500000000000455</v>
+        <v>7.4500000000000455</v>
       </c>
       <c r="C22" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="D22" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E22">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="F22">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G22">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H22">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A23">
-        <v>928.27086363636363</v>
+        <v>929.4308636363636</v>
       </c>
       <c r="B23">
-        <v>-2.6100000000000136</v>
+        <v>-1.4500000000000455</v>
       </c>
       <c r="C23" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="D23" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="E23">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="F23">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G23">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H23">
-        <v>8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A24">
-        <v>923.04900000000009</v>
+        <v>928.27086363636363</v>
       </c>
       <c r="B24">
-        <v>-28.659999999999968</v>
+        <v>-2.6100000000000136</v>
       </c>
       <c r="C24" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="D24" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="E24">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F24">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G24">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H24">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A25">
-        <v>919.69086363636359</v>
+        <v>911.94749999999999</v>
       </c>
       <c r="B25">
-        <v>-11.190000000000055</v>
+        <v>-69.710000000000036</v>
       </c>
       <c r="C25" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="D25" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="E25">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="F25">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G25">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H25">
-        <v>4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A26">
-        <v>911.94749999999999</v>
+        <v>906.11086363636366</v>
       </c>
       <c r="B26">
-        <v>-69.710000000000036</v>
+        <v>-24.769999999999982</v>
       </c>
       <c r="C26" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="D26" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="E26">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="F26">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G26">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H26">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A27">
-        <v>906.11086363636366</v>
+        <v>898.62086363636365</v>
       </c>
       <c r="B27">
-        <v>-24.769999999999982</v>
+        <v>-32.259999999999991</v>
       </c>
       <c r="C27" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="D27" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E27">
+        <v>11</v>
+      </c>
+      <c r="F27">
+        <v>2</v>
+      </c>
+      <c r="G27">
+        <v>2</v>
+      </c>
+      <c r="H27">
         <v>7</v>
-      </c>
-      <c r="F27">
-        <v>1</v>
-      </c>
-      <c r="G27">
-        <v>0</v>
-      </c>
-      <c r="H27">
-        <v>6</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.3">
@@ -1471,10 +1471,10 @@
         <v>-41.439999999999941</v>
       </c>
       <c r="C28" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="D28" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="E28">
         <v>7</v>
@@ -1497,10 +1497,10 @@
         <v>-59.940000000000055</v>
       </c>
       <c r="C29" t="s">
-        <v>10</v>
+        <v>71</v>
       </c>
       <c r="D29" t="s">
-        <v>12</v>
+        <v>72</v>
       </c>
       <c r="E29">
         <v>31</v>

--- a/Ranking_Data.xlsx
+++ b/Ranking_Data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="c:\Users\원영이\Desktop\ATL AUTO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{281A37ED-857D-4923-978E-4BD17FAD50E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{6171E380-D0D4-4782-8DD4-39BFF54F8F1B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-114" yWindow="-114" windowWidth="36727" windowHeight="20317" xr2:uid="{5CAA5E78-16DA-4BC0-9284-6E226C75FF81}"/>
+    <workbookView xWindow="314" yWindow="955" windowWidth="36185" windowHeight="19576" xr2:uid="{EB5D6DF8-0E7D-4EC6-B786-34D4968816A9}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -65,15 +65,21 @@
     <t>패</t>
   </si>
   <si>
+    <t>Voor</t>
+  </si>
+  <si>
+    <t>첼시</t>
+  </si>
+  <si>
     <t>UNIT</t>
   </si>
   <si>
+    <t>17시즌</t>
+  </si>
+  <si>
     <t>AS 로마</t>
   </si>
   <si>
-    <t>17시즌</t>
-  </si>
-  <si>
     <t>개포동덕배</t>
   </si>
   <si>
@@ -89,12 +95,6 @@
     <t>경기 수</t>
   </si>
   <si>
-    <t>Voor</t>
-  </si>
-  <si>
-    <t>첼시</t>
-  </si>
-  <si>
     <t>1부리그</t>
   </si>
   <si>
@@ -152,22 +152,28 @@
     <t>프랑크푸르트</t>
   </si>
   <si>
+    <t>ZD장인지참치</t>
+  </si>
+  <si>
+    <t>레버쿠젠</t>
+  </si>
+  <si>
+    <t>방덕</t>
+  </si>
+  <si>
+    <t>인테르</t>
+  </si>
+  <si>
     <t>호야국2인</t>
   </si>
   <si>
     <t>SSC 나폴리</t>
   </si>
   <si>
-    <t>ZD장인지참치</t>
-  </si>
-  <si>
-    <t>레버쿠젠</t>
-  </si>
-  <si>
-    <t>방덕</t>
-  </si>
-  <si>
-    <t>인테르</t>
+    <t>콩콩콩룔</t>
+  </si>
+  <si>
+    <t>라치오</t>
   </si>
   <si>
     <t>비주류중독</t>
@@ -176,12 +182,6 @@
     <t>셀틱 FC</t>
   </si>
   <si>
-    <t>콩콩콩룔</t>
-  </si>
-  <si>
-    <t>라치오</t>
-  </si>
-  <si>
     <t>여수가스</t>
   </si>
   <si>
@@ -206,28 +206,28 @@
     <t>경남 FC</t>
   </si>
   <si>
+    <t>셀래스틴</t>
+  </si>
+  <si>
+    <t>바르셀로나</t>
+  </si>
+  <si>
+    <t>0708ManUtd</t>
+  </si>
+  <si>
+    <t>레알 마드리드</t>
+  </si>
+  <si>
+    <t>용신</t>
+  </si>
+  <si>
+    <t>토트넘</t>
+  </si>
+  <si>
     <t>스페인전도사</t>
   </si>
   <si>
     <t>RC 셀타 비고</t>
-  </si>
-  <si>
-    <t>셀래스틴</t>
-  </si>
-  <si>
-    <t>바르셀로나</t>
-  </si>
-  <si>
-    <t>0708ManUtd</t>
-  </si>
-  <si>
-    <t>레알 마드리드</t>
-  </si>
-  <si>
-    <t>용신</t>
-  </si>
-  <si>
-    <t>토트넘</t>
   </si>
   <si>
     <t>Gucci차붐</t>
@@ -640,7 +640,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F7010920-4F4D-4D1C-B896-09D027111F1B}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{568F1821-E4A4-4868-A77F-3A1DB1C3F062}">
   <dimension ref="A1:O29"/>
   <sheetFormatPr defaultRowHeight="15.7" x14ac:dyDescent="0.3"/>
   <sheetData>
@@ -672,10 +672,10 @@
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A2">
-        <v>1155.4175</v>
+        <v>1222.1724999999999</v>
       </c>
       <c r="B2">
-        <v>124.59999999999991</v>
+        <v>97.950000000000045</v>
       </c>
       <c r="C2" t="s">
         <v>8</v>
@@ -684,39 +684,39 @@
         <v>9</v>
       </c>
       <c r="E2">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="F2">
+        <v>9</v>
+      </c>
+      <c r="G2">
+        <v>3</v>
+      </c>
+      <c r="H2">
+        <v>3</v>
+      </c>
+      <c r="J2" t="s">
+        <v>10</v>
+      </c>
+      <c r="L2" t="s">
+        <v>11</v>
+      </c>
+      <c r="M2" t="s">
         <v>12</v>
-      </c>
-      <c r="G2">
-        <v>4</v>
-      </c>
-      <c r="H2">
-        <v>3</v>
-      </c>
-      <c r="J2" t="s">
-        <v>8</v>
-      </c>
-      <c r="L2" t="s">
-        <v>10</v>
-      </c>
-      <c r="M2" t="s">
-        <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A3">
-        <v>1153.174</v>
+        <v>1157.5340000000001</v>
       </c>
       <c r="B3">
-        <v>38.309999999999945</v>
+        <v>42.670000000000073</v>
       </c>
       <c r="C3" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D3" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E3">
         <v>4</v>
@@ -731,13 +731,13 @@
         <v>0</v>
       </c>
       <c r="J3" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="K3" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="L3" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="M3" t="s">
         <v>5</v>
@@ -751,37 +751,37 @@
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A4">
-        <v>1128.3224999999998</v>
+        <v>1142.4875000000002</v>
       </c>
       <c r="B4">
-        <v>4.0999999999999091</v>
+        <v>111.67000000000007</v>
       </c>
       <c r="C4" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="D4" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="E4">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="F4">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="G4">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H4">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J4" t="s">
         <v>18</v>
       </c>
       <c r="K4">
-        <v>67.53</v>
+        <v>37.36999999999999</v>
       </c>
       <c r="L4">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="M4">
         <v>3</v>
@@ -790,15 +790,15 @@
         <v>2</v>
       </c>
       <c r="O4">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A5">
-        <v>1093.6675</v>
+        <v>1105.5274999999999</v>
       </c>
       <c r="B5">
-        <v>44.710000000000036</v>
+        <v>56.569999999999936</v>
       </c>
       <c r="C5" t="s">
         <v>19</v>
@@ -822,7 +822,7 @@
         <v>21</v>
       </c>
       <c r="K5">
-        <v>19.260000000000002</v>
+        <v>18.809999999999999</v>
       </c>
       <c r="L5">
         <v>1</v>
@@ -839,10 +839,10 @@
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A6">
-        <v>1090.7725000000003</v>
+        <v>1098.7825000000003</v>
       </c>
       <c r="B6">
-        <v>51.160000000000082</v>
+        <v>59.170000000000073</v>
       </c>
       <c r="C6" t="s">
         <v>22</v>
@@ -866,7 +866,7 @@
         <v>24</v>
       </c>
       <c r="K6">
-        <v>37.81</v>
+        <v>55.489999999999995</v>
       </c>
       <c r="L6">
         <v>12</v>
@@ -883,10 +883,10 @@
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A7">
-        <v>1083.2649999999999</v>
+        <v>1079.865</v>
       </c>
       <c r="B7">
-        <v>39.099999999999909</v>
+        <v>35.700000000000045</v>
       </c>
       <c r="C7" t="s">
         <v>25</v>
@@ -895,16 +895,16 @@
         <v>26</v>
       </c>
       <c r="E7">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F7">
         <v>2</v>
       </c>
       <c r="G7">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H7">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J7" t="s">
         <v>27</v>
@@ -927,10 +927,10 @@
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A8">
-        <v>1035.0690000000002</v>
+        <v>1045.4490000000003</v>
       </c>
       <c r="B8">
-        <v>-5.4500000000000455</v>
+        <v>4.9300000000000637</v>
       </c>
       <c r="C8" t="s">
         <v>28</v>
@@ -954,10 +954,10 @@
         <v>30</v>
       </c>
       <c r="K8">
-        <v>124.60000000000001</v>
+        <v>111.66999999999999</v>
       </c>
       <c r="L8">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="M8">
         <v>12</v>
@@ -966,15 +966,15 @@
         <v>4</v>
       </c>
       <c r="O8">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A9">
-        <v>1029.7650000000001</v>
+        <v>1040.3150000000001</v>
       </c>
       <c r="B9">
-        <v>37.180000000000064</v>
+        <v>47.730000000000018</v>
       </c>
       <c r="C9" t="s">
         <v>31</v>
@@ -997,10 +997,10 @@
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A10">
-        <v>1027.5374999999999</v>
+        <v>1028.1575</v>
       </c>
       <c r="B10">
-        <v>-26.680000000000064</v>
+        <v>-26.059999999999945</v>
       </c>
       <c r="C10" t="s">
         <v>33</v>
@@ -1020,13 +1020,19 @@
       <c r="H10">
         <v>2</v>
       </c>
+      <c r="J10">
+        <v>1</v>
+      </c>
+      <c r="K10">
+        <v>38</v>
+      </c>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A11">
-        <v>1018.7049999999998</v>
+        <v>1023.0649999999998</v>
       </c>
       <c r="B11">
-        <v>-18.600000000000023</v>
+        <v>-14.240000000000009</v>
       </c>
       <c r="C11" t="s">
         <v>35</v>
@@ -1046,13 +1052,19 @@
       <c r="H11">
         <v>5</v>
       </c>
+      <c r="J11">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="K11">
+        <v>46.750000000000007</v>
+      </c>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A12">
-        <v>1001.8340000000001</v>
+        <v>1013.4508636363637</v>
       </c>
       <c r="B12">
-        <v>0</v>
+        <v>82.57000000000005</v>
       </c>
       <c r="C12" t="s">
         <v>37</v>
@@ -1061,24 +1073,30 @@
         <v>38</v>
       </c>
       <c r="E12">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F12">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="G12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H12">
-        <v>0</v>
+        <v>7</v>
+      </c>
+      <c r="J12">
+        <v>1.2</v>
+      </c>
+      <c r="K12">
+        <v>55.489999999999995</v>
       </c>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A13">
-        <v>998.58086363636369</v>
+        <v>1007.3890000000001</v>
       </c>
       <c r="B13">
-        <v>67.700000000000045</v>
+        <v>-19.480000000000018</v>
       </c>
       <c r="C13" t="s">
         <v>39</v>
@@ -1087,24 +1105,24 @@
         <v>40</v>
       </c>
       <c r="E13">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="F13">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="G13">
         <v>1</v>
       </c>
       <c r="H13">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A14">
-        <v>995.99900000000014</v>
+        <v>1001.8340000000001</v>
       </c>
       <c r="B14">
-        <v>-30.870000000000005</v>
+        <v>0</v>
       </c>
       <c r="C14" t="s">
         <v>41</v>
@@ -1113,24 +1131,24 @@
         <v>42</v>
       </c>
       <c r="E14">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="F14">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G14">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H14">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A15">
-        <v>974.53086363636362</v>
+        <v>1001.47</v>
       </c>
       <c r="B15">
-        <v>43.649999999999977</v>
+        <v>-5.6299999999999955</v>
       </c>
       <c r="C15" t="s">
         <v>43</v>
@@ -1139,24 +1157,24 @@
         <v>44</v>
       </c>
       <c r="E15">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="F15">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="G15">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H15">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A16">
-        <v>966.74</v>
+        <v>992.59086363636368</v>
       </c>
       <c r="B16">
-        <v>-40.360000000000014</v>
+        <v>61.710000000000036</v>
       </c>
       <c r="C16" t="s">
         <v>45</v>
@@ -1165,24 +1183,24 @@
         <v>46</v>
       </c>
       <c r="E16">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="F16">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G16">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H16">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A17">
-        <v>965.73086363636367</v>
+        <v>974.47086363636367</v>
       </c>
       <c r="B17">
-        <v>34.850000000000023</v>
+        <v>43.590000000000032</v>
       </c>
       <c r="C17" t="s">
         <v>47</v>
@@ -1191,24 +1209,24 @@
         <v>48</v>
       </c>
       <c r="E17">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="F17">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G17">
         <v>1</v>
       </c>
       <c r="H17">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A18">
-        <v>953.15086363636362</v>
+        <v>962.26086363636364</v>
       </c>
       <c r="B18">
-        <v>22.269999999999982</v>
+        <v>31.379999999999995</v>
       </c>
       <c r="C18" t="s">
         <v>49</v>
@@ -1231,10 +1249,10 @@
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A19">
-        <v>948.87</v>
+        <v>955.8</v>
       </c>
       <c r="B19">
-        <v>-21.149999999999977</v>
+        <v>-14.220000000000027</v>
       </c>
       <c r="C19" t="s">
         <v>51</v>
@@ -1257,10 +1275,10 @@
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A20">
-        <v>941.61900000000003</v>
+        <v>948.84900000000005</v>
       </c>
       <c r="B20">
-        <v>-10.090000000000032</v>
+        <v>-2.8600000000000136</v>
       </c>
       <c r="C20" t="s">
         <v>53</v>
@@ -1283,10 +1301,10 @@
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A21">
-        <v>941.3208636363637</v>
+        <v>946.0708636363637</v>
       </c>
       <c r="B21">
-        <v>10.440000000000055</v>
+        <v>15.190000000000055</v>
       </c>
       <c r="C21" t="s">
         <v>55</v>
@@ -1295,24 +1313,24 @@
         <v>56</v>
       </c>
       <c r="E21">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="F21">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G21">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H21">
-        <v>10</v>
+        <v>3</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A22">
-        <v>938.33086363636369</v>
+        <v>929.3208636363637</v>
       </c>
       <c r="B22">
-        <v>7.4500000000000455</v>
+        <v>-1.5599999999999454</v>
       </c>
       <c r="C22" t="s">
         <v>57</v>
@@ -1321,24 +1339,24 @@
         <v>58</v>
       </c>
       <c r="E22">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="F22">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G22">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H22">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A23">
-        <v>929.4308636363636</v>
+        <v>927.1808636363636</v>
       </c>
       <c r="B23">
-        <v>-1.4500000000000455</v>
+        <v>-3.7000000000000455</v>
       </c>
       <c r="C23" t="s">
         <v>59</v>
@@ -1347,24 +1365,24 @@
         <v>60</v>
       </c>
       <c r="E23">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="F23">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G23">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H23">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A24">
-        <v>928.27086363636363</v>
+        <v>923.37086363636365</v>
       </c>
       <c r="B24">
-        <v>-2.6100000000000136</v>
+        <v>-7.5099999999999909</v>
       </c>
       <c r="C24" t="s">
         <v>61</v>
@@ -1373,24 +1391,24 @@
         <v>62</v>
       </c>
       <c r="E24">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="F24">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="G24">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H24">
-        <v>8</v>
+        <v>13</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A25">
-        <v>911.94749999999999</v>
+        <v>922.16750000000002</v>
       </c>
       <c r="B25">
-        <v>-69.710000000000036</v>
+        <v>-59.490000000000009</v>
       </c>
       <c r="C25" t="s">
         <v>63</v>
@@ -1413,10 +1431,10 @@
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A26">
-        <v>906.11086363636366</v>
+        <v>906.37086363636365</v>
       </c>
       <c r="B26">
-        <v>-24.769999999999982</v>
+        <v>-24.509999999999991</v>
       </c>
       <c r="C26" t="s">
         <v>65</v>
@@ -1439,10 +1457,10 @@
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A27">
-        <v>898.62086363636365</v>
+        <v>899.15086363636362</v>
       </c>
       <c r="B27">
-        <v>-32.259999999999991</v>
+        <v>-31.730000000000018</v>
       </c>
       <c r="C27" t="s">
         <v>67</v>
@@ -1465,10 +1483,10 @@
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A28">
-        <v>889.4408636363637</v>
+        <v>894.03086363636362</v>
       </c>
       <c r="B28">
-        <v>-41.439999999999941</v>
+        <v>-36.850000000000023</v>
       </c>
       <c r="C28" t="s">
         <v>69</v>
@@ -1491,10 +1509,10 @@
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A29">
-        <v>874.28399999999999</v>
+        <v>879.42400000000009</v>
       </c>
       <c r="B29">
-        <v>-59.940000000000055</v>
+        <v>-54.799999999999955</v>
       </c>
       <c r="C29" t="s">
         <v>71</v>

--- a/Ranking_Data.xlsx
+++ b/Ranking_Data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="c:\Users\원영이\Desktop\ATL AUTO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{6171E380-D0D4-4782-8DD4-39BFF54F8F1B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{9708DFE1-BF38-4C83-935F-1D84EE545B2F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="314" yWindow="955" windowWidth="36185" windowHeight="19576" xr2:uid="{EB5D6DF8-0E7D-4EC6-B786-34D4968816A9}"/>
+    <workbookView xWindow="314" yWindow="770" windowWidth="36185" windowHeight="19575" xr2:uid="{5D7B50A9-F110-441C-8191-B5B058D3A024}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -125,21 +125,21 @@
     <t>UEFA Tournament</t>
   </si>
   <si>
+    <t>앙쿠</t>
+  </si>
+  <si>
+    <t>아틀레티코 마드리드</t>
+  </si>
+  <si>
+    <t>전체 합계</t>
+  </si>
+  <si>
     <t>오스트리아</t>
   </si>
   <si>
     <t>마인츠</t>
   </si>
   <si>
-    <t>전체 합계</t>
-  </si>
-  <si>
-    <t>앙쿠</t>
-  </si>
-  <si>
-    <t>아틀레티코 마드리드</t>
-  </si>
-  <si>
     <t>킹왕두</t>
   </si>
   <si>
@@ -182,18 +182,18 @@
     <t>셀틱 FC</t>
   </si>
   <si>
+    <t>suma수마</t>
+  </si>
+  <si>
+    <t>ACF 피오렌티나</t>
+  </si>
+  <si>
     <t>여수가스</t>
   </si>
   <si>
     <t>AS 모나코</t>
   </si>
   <si>
-    <t>suma수마</t>
-  </si>
-  <si>
-    <t>ACF 피오렌티나</t>
-  </si>
-  <si>
     <t>Gucci와퍼</t>
   </si>
   <si>
@@ -236,28 +236,28 @@
     <t>전북 현대 모터스</t>
   </si>
   <si>
+    <t>겐지간지</t>
+  </si>
+  <si>
+    <t>파리 생제르맹</t>
+  </si>
+  <si>
+    <t>A지냐크</t>
+  </si>
+  <si>
+    <t>올랭피크 마르세유</t>
+  </si>
+  <si>
+    <t>Legend독수리</t>
+  </si>
+  <si>
+    <t>맨체스터 유나이티드</t>
+  </si>
+  <si>
     <t>ShangHaiPortFC</t>
   </si>
   <si>
     <t>상하이 선화</t>
-  </si>
-  <si>
-    <t>A지냐크</t>
-  </si>
-  <si>
-    <t>올랭피크 마르세유</t>
-  </si>
-  <si>
-    <t>겐지간지</t>
-  </si>
-  <si>
-    <t>파리 생제르맹</t>
-  </si>
-  <si>
-    <t>Legend독수리</t>
-  </si>
-  <si>
-    <t>맨체스터 유나이티드</t>
   </si>
 </sst>
 </file>
@@ -640,7 +640,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{568F1821-E4A4-4868-A77F-3A1DB1C3F062}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{538FC0CF-9E46-4E65-81E8-6AC8D2407C35}">
   <dimension ref="A1:O29"/>
   <sheetFormatPr defaultRowHeight="15.7" x14ac:dyDescent="0.3"/>
   <sheetData>
@@ -927,10 +927,10 @@
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A8">
-        <v>1045.4490000000003</v>
+        <v>1067.645</v>
       </c>
       <c r="B8">
-        <v>4.9300000000000637</v>
+        <v>75.059999999999945</v>
       </c>
       <c r="C8" t="s">
         <v>28</v>
@@ -939,16 +939,16 @@
         <v>29</v>
       </c>
       <c r="E8">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="F8">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G8">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H8">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="J8" t="s">
         <v>30</v>
@@ -971,10 +971,10 @@
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A9">
-        <v>1040.3150000000001</v>
+        <v>1045.4490000000003</v>
       </c>
       <c r="B9">
-        <v>47.730000000000018</v>
+        <v>4.9300000000000637</v>
       </c>
       <c r="C9" t="s">
         <v>31</v>
@@ -983,16 +983,16 @@
         <v>32</v>
       </c>
       <c r="E9">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="F9">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="G9">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H9">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.3">
@@ -1197,10 +1197,10 @@
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A17">
-        <v>974.47086363636367</v>
+        <v>977.15086363636362</v>
       </c>
       <c r="B17">
-        <v>43.590000000000032</v>
+        <v>46.269999999999982</v>
       </c>
       <c r="C17" t="s">
         <v>47</v>
@@ -1209,24 +1209,24 @@
         <v>48</v>
       </c>
       <c r="E17">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="F17">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="G17">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H17">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A18">
-        <v>962.26086363636364</v>
+        <v>974.47086363636367</v>
       </c>
       <c r="B18">
-        <v>31.379999999999995</v>
+        <v>43.590000000000032</v>
       </c>
       <c r="C18" t="s">
         <v>49</v>
@@ -1235,16 +1235,16 @@
         <v>50</v>
       </c>
       <c r="E18">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="F18">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G18">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H18">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.3">
@@ -1301,10 +1301,10 @@
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A21">
-        <v>946.0708636363637</v>
+        <v>944.42086363636361</v>
       </c>
       <c r="B21">
-        <v>15.190000000000055</v>
+        <v>13.539999999999964</v>
       </c>
       <c r="C21" t="s">
         <v>55</v>
@@ -1313,16 +1313,16 @@
         <v>56</v>
       </c>
       <c r="E21">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F21">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G21">
         <v>2</v>
       </c>
       <c r="H21">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.3">
@@ -1431,10 +1431,10 @@
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A26">
-        <v>906.37086363636365</v>
+        <v>894.03086363636362</v>
       </c>
       <c r="B26">
-        <v>-24.509999999999991</v>
+        <v>-36.850000000000023</v>
       </c>
       <c r="C26" t="s">
         <v>65</v>
@@ -1457,10 +1457,10 @@
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A27">
-        <v>899.15086363636362</v>
+        <v>891.67086363636361</v>
       </c>
       <c r="B27">
-        <v>-31.730000000000018</v>
+        <v>-39.210000000000036</v>
       </c>
       <c r="C27" t="s">
         <v>67</v>
@@ -1469,7 +1469,7 @@
         <v>68</v>
       </c>
       <c r="E27">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F27">
         <v>2</v>
@@ -1478,15 +1478,15 @@
         <v>2</v>
       </c>
       <c r="H27">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A28">
-        <v>894.03086363636362</v>
+        <v>881.654</v>
       </c>
       <c r="B28">
-        <v>-36.850000000000023</v>
+        <v>-52.57000000000005</v>
       </c>
       <c r="C28" t="s">
         <v>69</v>
@@ -1495,24 +1495,24 @@
         <v>70</v>
       </c>
       <c r="E28">
-        <v>7</v>
+        <v>35</v>
       </c>
       <c r="F28">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="G28">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H28">
-        <v>6</v>
+        <v>22</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A29">
-        <v>879.42400000000009</v>
+        <v>874.17086363636361</v>
       </c>
       <c r="B29">
-        <v>-54.799999999999955</v>
+        <v>-56.710000000000036</v>
       </c>
       <c r="C29" t="s">
         <v>71</v>
@@ -1521,16 +1521,16 @@
         <v>72</v>
       </c>
       <c r="E29">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="F29">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="G29">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H29">
-        <v>20</v>
+        <v>13</v>
       </c>
     </row>
   </sheetData>

--- a/Ranking_Data.xlsx
+++ b/Ranking_Data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="c:\Users\원영이\Desktop\ATL AUTO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{4AC47324-B063-4CEF-BB5B-A2F949262A2E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{96524FC5-A71D-4670-8D60-CE327269554A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="314" yWindow="955" windowWidth="36185" windowHeight="19576" xr2:uid="{4A172D24-2D9B-4568-A3F0-111F83EBA2FF}"/>
+    <workbookView xWindow="314" yWindow="955" windowWidth="36185" windowHeight="19576" xr2:uid="{9D77D0E4-5AFB-41CF-A462-4D5AC083CE51}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="90">
   <si>
     <t>17th ELO</t>
   </si>
@@ -71,39 +71,39 @@
     <t>첼시</t>
   </si>
   <si>
+    <t>UNIT</t>
+  </si>
+  <si>
+    <t>17시즌</t>
+  </si>
+  <si>
+    <t>AS 로마</t>
+  </si>
+  <si>
+    <t>개포동덕배</t>
+  </si>
+  <si>
+    <t>바이에른 뮌헨</t>
+  </si>
+  <si>
+    <t>대회종류</t>
+  </si>
+  <si>
+    <t>ELO 변동값</t>
+  </si>
+  <si>
+    <t>경기 수</t>
+  </si>
+  <si>
+    <t>1부리그</t>
+  </si>
+  <si>
     <t>은안</t>
   </si>
   <si>
-    <t>17시즌</t>
-  </si>
-  <si>
     <t>맨체스터 시티</t>
   </si>
   <si>
-    <t>개포동덕배</t>
-  </si>
-  <si>
-    <t>바이에른 뮌헨</t>
-  </si>
-  <si>
-    <t>대회종류</t>
-  </si>
-  <si>
-    <t>ELO 변동값</t>
-  </si>
-  <si>
-    <t>경기 수</t>
-  </si>
-  <si>
-    <t>UNIT</t>
-  </si>
-  <si>
-    <t>AS 로마</t>
-  </si>
-  <si>
-    <t>1부리그</t>
-  </si>
-  <si>
     <t>FA컵</t>
   </si>
   <si>
@@ -113,7 +113,7 @@
     <t>AC 밀란</t>
   </si>
   <si>
-    <t>UEFA_C조</t>
+    <t>UEFA_A조</t>
   </si>
   <si>
     <t>Special블루</t>
@@ -140,34 +140,46 @@
     <t>마인츠</t>
   </si>
   <si>
+    <t>킹왕두</t>
+  </si>
+  <si>
+    <t>리버풀</t>
+  </si>
+  <si>
+    <t>아들러</t>
+  </si>
+  <si>
+    <t>프랑크푸르트</t>
+  </si>
+  <si>
+    <t>2부리그</t>
+  </si>
+  <si>
+    <t>호야국2인</t>
+  </si>
+  <si>
+    <t>SSC 나폴리</t>
+  </si>
+  <si>
+    <t>3부리그</t>
+  </si>
+  <si>
+    <t>콩콩콩룔</t>
+  </si>
+  <si>
+    <t>라치오</t>
+  </si>
+  <si>
+    <t>FA컵_결승전</t>
+  </si>
+  <si>
     <t>비주류중독</t>
   </si>
   <si>
     <t>셀틱 FC</t>
   </si>
   <si>
-    <t>킹왕두</t>
-  </si>
-  <si>
-    <t>리버풀</t>
-  </si>
-  <si>
-    <t>호야국2인</t>
-  </si>
-  <si>
-    <t>SSC 나폴리</t>
-  </si>
-  <si>
-    <t>아들러</t>
-  </si>
-  <si>
-    <t>프랑크푸르트</t>
-  </si>
-  <si>
-    <t>콩콩콩룔</t>
-  </si>
-  <si>
-    <t>라치오</t>
+    <t>FA컵_4강</t>
   </si>
   <si>
     <t>ZD장인지참치</t>
@@ -176,22 +188,43 @@
     <t>레버쿠젠</t>
   </si>
   <si>
+    <t>FA컵_8강</t>
+  </si>
+  <si>
     <t>셀래스틴</t>
   </si>
   <si>
     <t>바르셀로나</t>
   </si>
   <si>
+    <t>FA컵_16강</t>
+  </si>
+  <si>
+    <t>방덕</t>
+  </si>
+  <si>
+    <t>인테르</t>
+  </si>
+  <si>
+    <t>FA컵_32강</t>
+  </si>
+  <si>
     <t>여수가스</t>
   </si>
   <si>
     <t>AS 모나코</t>
   </si>
   <si>
-    <t>방덕</t>
-  </si>
-  <si>
-    <t>인테르</t>
+    <t>UEFA</t>
+  </si>
+  <si>
+    <t>Gucci와퍼</t>
+  </si>
+  <si>
+    <t>함부르크SV</t>
+  </si>
+  <si>
+    <t>UCL_결승전</t>
   </si>
   <si>
     <t>suma수마</t>
@@ -200,10 +233,7 @@
     <t>ACF 피오렌티나</t>
   </si>
   <si>
-    <t>Gucci와퍼</t>
-  </si>
-  <si>
-    <t>함부르크SV</t>
+    <t>UCL_4강</t>
   </si>
   <si>
     <t>경남FC가즈아</t>
@@ -212,16 +242,25 @@
     <t>경남 FC</t>
   </si>
   <si>
+    <t>UCL_8강</t>
+  </si>
+  <si>
+    <t>용신</t>
+  </si>
+  <si>
+    <t>토트넘</t>
+  </si>
+  <si>
+    <t>UEL_FINAL</t>
+  </si>
+  <si>
     <t>0708ManUtd</t>
   </si>
   <si>
     <t>레알 마드리드</t>
   </si>
   <si>
-    <t>용신</t>
-  </si>
-  <si>
-    <t>토트넘</t>
+    <t>UEL_4강</t>
   </si>
   <si>
     <t>스페인전도사</t>
@@ -230,22 +269,34 @@
     <t>RC 셀타 비고</t>
   </si>
   <si>
+    <t>UEL_8강</t>
+  </si>
+  <si>
+    <t>A지냐크</t>
+  </si>
+  <si>
+    <t>올랭피크 마르세유</t>
+  </si>
+  <si>
+    <t>UECL_FINAL</t>
+  </si>
+  <si>
     <t>Gucci차붐</t>
   </si>
   <si>
     <t>전북 현대 모터스</t>
   </si>
   <si>
-    <t>A지냐크</t>
-  </si>
-  <si>
-    <t>올랭피크 마르세유</t>
+    <t>UECL_4강</t>
   </si>
   <si>
     <t>Legend독수리</t>
   </si>
   <si>
     <t>맨체스터 유나이티드</t>
+  </si>
+  <si>
+    <t>UECL_8강</t>
   </si>
   <si>
     <t>ShangHaiPortFC</t>
@@ -640,7 +691,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D4596F90-011A-4974-830C-E45C24A40E0E}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C060934B-E56B-4845-B081-5FE82B00DA6B}">
   <dimension ref="A1:O29"/>
   <sheetFormatPr defaultRowHeight="15.7" x14ac:dyDescent="0.3"/>
   <sheetData>
@@ -672,10 +723,10 @@
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A2">
-        <v>1222.1724999999999</v>
+        <v>1214.9424999999999</v>
       </c>
       <c r="B2">
-        <v>97.950000000000045</v>
+        <v>90.720000000000027</v>
       </c>
       <c r="C2" t="s">
         <v>8</v>
@@ -707,10 +758,10 @@
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A3">
-        <v>1197.374</v>
+        <v>1173.3240000000001</v>
       </c>
       <c r="B3">
-        <v>82.509999999999991</v>
+        <v>58.460000000000036</v>
       </c>
       <c r="C3" t="s">
         <v>13</v>
@@ -719,16 +770,16 @@
         <v>14</v>
       </c>
       <c r="E3">
+        <v>12</v>
+      </c>
+      <c r="F3">
         <v>10</v>
-      </c>
-      <c r="F3">
-        <v>9</v>
       </c>
       <c r="G3">
         <v>1</v>
       </c>
       <c r="H3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J3" t="s">
         <v>15</v>
@@ -751,16 +802,16 @@
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A4">
-        <v>1142.4875000000002</v>
+        <v>1130.2275000000002</v>
       </c>
       <c r="B4">
-        <v>111.67000000000007</v>
+        <v>99.410000000000082</v>
       </c>
       <c r="C4" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="D4" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="E4">
         <v>21</v>
@@ -775,36 +826,36 @@
         <v>5</v>
       </c>
       <c r="J4" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="K4">
-        <v>56.839999999999989</v>
+        <v>39.370000000000005</v>
       </c>
       <c r="L4">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="M4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O4">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A5">
-        <v>1108.1849999999999</v>
+        <v>1097.5650000000001</v>
       </c>
       <c r="B5">
-        <v>64.019999999999982</v>
+        <v>53.400000000000091</v>
       </c>
       <c r="C5" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="D5" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="E5">
         <v>13</v>
@@ -822,27 +873,27 @@
         <v>21</v>
       </c>
       <c r="K5">
-        <v>-21.14</v>
+        <v>22.51</v>
       </c>
       <c r="L5">
         <v>1</v>
       </c>
       <c r="M5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N5">
         <v>0</v>
       </c>
       <c r="O5">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A6">
-        <v>1105.5274999999999</v>
+        <v>1094.4775</v>
       </c>
       <c r="B6">
-        <v>56.569999999999936</v>
+        <v>45.519999999999982</v>
       </c>
       <c r="C6" t="s">
         <v>22</v>
@@ -866,27 +917,27 @@
         <v>24</v>
       </c>
       <c r="K6">
-        <v>28.32</v>
+        <v>37.53</v>
       </c>
       <c r="L6">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="M6">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="N6">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A7">
-        <v>1098.7825000000003</v>
+        <v>1090.7825000000003</v>
       </c>
       <c r="B7">
-        <v>59.170000000000073</v>
+        <v>51.170000000000073</v>
       </c>
       <c r="C7" t="s">
         <v>25</v>
@@ -927,10 +978,10 @@
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A8">
-        <v>1067.645</v>
+        <v>1058.075</v>
       </c>
       <c r="B8">
-        <v>75.059999999999945</v>
+        <v>65.490000000000009</v>
       </c>
       <c r="C8" t="s">
         <v>28</v>
@@ -954,27 +1005,27 @@
         <v>30</v>
       </c>
       <c r="K8">
-        <v>64.019999999999982</v>
+        <v>99.410000000000011</v>
       </c>
       <c r="L8">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="M8">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="N8">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O8">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A9">
-        <v>1045.4490000000003</v>
+        <v>1037.0890000000002</v>
       </c>
       <c r="B9">
-        <v>4.9300000000000637</v>
+        <v>-3.4300000000000637</v>
       </c>
       <c r="C9" t="s">
         <v>31</v>
@@ -997,10 +1048,10 @@
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A10">
-        <v>1029.8208636363636</v>
+        <v>1027.7774999999999</v>
       </c>
       <c r="B10">
-        <v>98.939999999999941</v>
+        <v>-26.440000000000055</v>
       </c>
       <c r="C10" t="s">
         <v>33</v>
@@ -1009,30 +1060,30 @@
         <v>34</v>
       </c>
       <c r="E10">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="F10">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="G10">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H10">
-        <v>7</v>
-      </c>
-      <c r="J10">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="J10" t="s">
+        <v>18</v>
       </c>
       <c r="K10">
-        <v>38</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A11">
-        <v>1028.1575</v>
+        <v>1018.8149999999998</v>
       </c>
       <c r="B11">
-        <v>-26.059999999999945</v>
+        <v>-18.490000000000009</v>
       </c>
       <c r="C11" t="s">
         <v>35</v>
@@ -1041,36 +1092,36 @@
         <v>36</v>
       </c>
       <c r="E11">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="F11">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G11">
         <v>0</v>
       </c>
       <c r="H11">
-        <v>2</v>
-      </c>
-      <c r="J11">
-        <v>1.1000000000000001</v>
+        <v>5</v>
+      </c>
+      <c r="J11" t="s">
+        <v>37</v>
       </c>
       <c r="K11">
-        <v>46.750000000000007</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A12">
-        <v>1023.144</v>
+        <v>1018.484</v>
       </c>
       <c r="B12">
-        <v>21.309999999999945</v>
+        <v>16.649999999999977</v>
       </c>
       <c r="C12" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D12" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E12">
         <v>4</v>
@@ -1084,103 +1135,121 @@
       <c r="H12">
         <v>1</v>
       </c>
-      <c r="J12">
-        <v>1.2</v>
+      <c r="J12" t="s">
+        <v>40</v>
       </c>
       <c r="K12">
-        <v>55.489999999999995</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A13">
-        <v>1023.0649999999998</v>
+        <v>1017.33</v>
       </c>
       <c r="B13">
-        <v>-14.240000000000009</v>
+        <v>10.230000000000018</v>
       </c>
       <c r="C13" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D13" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="E13">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F13">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H13">
         <v>5</v>
       </c>
+      <c r="J13" t="s">
+        <v>43</v>
+      </c>
+      <c r="K13">
+        <v>2.1</v>
+      </c>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A14">
-        <v>1001.47</v>
+        <v>1016.5408636363636</v>
       </c>
       <c r="B14">
-        <v>-5.6299999999999955</v>
+        <v>85.659999999999968</v>
       </c>
       <c r="C14" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="D14" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="E14">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="F14">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="G14">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H14">
-        <v>3</v>
+        <v>7</v>
+      </c>
+      <c r="J14" t="s">
+        <v>46</v>
+      </c>
+      <c r="K14">
+        <v>1.9</v>
       </c>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A15">
-        <v>996.91086363636362</v>
+        <v>1002.3108636363636</v>
       </c>
       <c r="B15">
-        <v>66.029999999999973</v>
+        <v>71.42999999999995</v>
       </c>
       <c r="C15" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="D15" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="E15">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="F15">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G15">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H15">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="J15" t="s">
+        <v>49</v>
+      </c>
+      <c r="K15">
+        <v>1.7</v>
       </c>
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A16">
-        <v>987.50086363636365</v>
+        <v>973.90086363636362</v>
       </c>
       <c r="B16">
-        <v>56.620000000000005</v>
+        <v>43.019999999999982</v>
       </c>
       <c r="C16" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="D16" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="E16">
         <v>12</v>
@@ -1194,123 +1263,153 @@
       <c r="H16">
         <v>4</v>
       </c>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J16" t="s">
+        <v>52</v>
+      </c>
+      <c r="K16">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A17">
-        <v>981.77086363636363</v>
+        <v>962.12900000000013</v>
       </c>
       <c r="B17">
-        <v>50.889999999999986</v>
+        <v>-64.740000000000009</v>
       </c>
       <c r="C17" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="D17" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="E17">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="F17">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="G17">
         <v>1</v>
       </c>
       <c r="H17">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
+        <v>7</v>
+      </c>
+      <c r="J17" t="s">
+        <v>55</v>
+      </c>
+      <c r="K17">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A18">
-        <v>973.44900000000018</v>
+        <v>952.13086363636364</v>
       </c>
       <c r="B18">
-        <v>-53.419999999999959</v>
+        <v>21.25</v>
       </c>
       <c r="C18" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="D18" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="E18">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="F18">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="G18">
+        <v>2</v>
+      </c>
+      <c r="H18">
+        <v>8</v>
+      </c>
+      <c r="J18" t="s">
+        <v>58</v>
+      </c>
+      <c r="K18">
         <v>1</v>
       </c>
-      <c r="H18">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A19">
-        <v>957.12086363636365</v>
+        <v>949.25</v>
       </c>
       <c r="B19">
-        <v>26.240000000000009</v>
+        <v>-20.769999999999982</v>
       </c>
       <c r="C19" t="s">
-        <v>51</v>
+        <v>59</v>
       </c>
       <c r="D19" t="s">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="E19">
+        <v>5</v>
+      </c>
+      <c r="F19">
+        <v>2</v>
+      </c>
+      <c r="G19">
+        <v>0</v>
+      </c>
+      <c r="H19">
+        <v>3</v>
+      </c>
+      <c r="J19" t="s">
+        <v>61</v>
+      </c>
+      <c r="K19">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A20">
+        <v>949.20086363636369</v>
+      </c>
+      <c r="B20">
+        <v>18.32000000000005</v>
+      </c>
+      <c r="C20" t="s">
+        <v>62</v>
+      </c>
+      <c r="D20" t="s">
+        <v>63</v>
+      </c>
+      <c r="E20">
         <v>29</v>
       </c>
-      <c r="F19">
+      <c r="F20">
         <v>16</v>
       </c>
-      <c r="G19">
-        <v>2</v>
-      </c>
-      <c r="H19">
+      <c r="G20">
+        <v>2</v>
+      </c>
+      <c r="H20">
         <v>11</v>
       </c>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A20">
-        <v>955.8</v>
-      </c>
-      <c r="B20">
-        <v>-14.220000000000027</v>
-      </c>
-      <c r="C20" t="s">
-        <v>53</v>
-      </c>
-      <c r="D20" t="s">
-        <v>54</v>
-      </c>
-      <c r="E20">
-        <v>5</v>
-      </c>
-      <c r="F20">
-        <v>2</v>
-      </c>
-      <c r="G20">
-        <v>0</v>
-      </c>
-      <c r="H20">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J20" t="s">
+        <v>64</v>
+      </c>
+      <c r="K20">
+        <v>1.7</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A21">
-        <v>948.84900000000005</v>
+        <v>947.70900000000006</v>
       </c>
       <c r="B21">
-        <v>-2.8600000000000136</v>
+        <v>-4</v>
       </c>
       <c r="C21" t="s">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="D21" t="s">
-        <v>56</v>
+        <v>66</v>
       </c>
       <c r="E21">
         <v>13</v>
@@ -1324,71 +1423,89 @@
       <c r="H21">
         <v>5</v>
       </c>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J21" t="s">
+        <v>67</v>
+      </c>
+      <c r="K21">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A22">
-        <v>936.51086363636364</v>
+        <v>930.88086363636364</v>
       </c>
       <c r="B22">
-        <v>5.6299999999999955</v>
+        <v>0</v>
       </c>
       <c r="C22" t="s">
-        <v>57</v>
+        <v>68</v>
       </c>
       <c r="D22" t="s">
-        <v>58</v>
+        <v>69</v>
       </c>
       <c r="E22">
+        <v>11</v>
+      </c>
+      <c r="F22">
+        <v>3</v>
+      </c>
+      <c r="G22">
+        <v>0</v>
+      </c>
+      <c r="H22">
+        <v>8</v>
+      </c>
+      <c r="J22" t="s">
+        <v>70</v>
+      </c>
+      <c r="K22">
+        <v>1.7</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A23">
+        <v>930.37086363636365</v>
+      </c>
+      <c r="B23">
+        <v>-0.50999999999999091</v>
+      </c>
+      <c r="C23" t="s">
+        <v>71</v>
+      </c>
+      <c r="D23" t="s">
+        <v>72</v>
+      </c>
+      <c r="E23">
         <v>7</v>
       </c>
-      <c r="F22">
+      <c r="F23">
         <v>1</v>
       </c>
-      <c r="G22">
-        <v>3</v>
-      </c>
-      <c r="H22">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A23">
-        <v>927.1808636363636</v>
-      </c>
-      <c r="B23">
-        <v>-3.7000000000000455</v>
-      </c>
-      <c r="C23" t="s">
-        <v>59</v>
-      </c>
-      <c r="D23" t="s">
-        <v>60</v>
-      </c>
-      <c r="E23">
-        <v>11</v>
-      </c>
-      <c r="F23">
-        <v>3</v>
-      </c>
       <c r="G23">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H23">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
+        <v>3</v>
+      </c>
+      <c r="J23" t="s">
+        <v>73</v>
+      </c>
+      <c r="K23">
+        <v>1.4</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A24">
-        <v>911.04086363636361</v>
+        <v>903.50086363636365</v>
       </c>
       <c r="B24">
-        <v>-19.840000000000032</v>
+        <v>-27.379999999999995</v>
       </c>
       <c r="C24" t="s">
-        <v>61</v>
+        <v>74</v>
       </c>
       <c r="D24" t="s">
-        <v>62</v>
+        <v>75</v>
       </c>
       <c r="E24">
         <v>25</v>
@@ -1402,71 +1519,89 @@
       <c r="H24">
         <v>15</v>
       </c>
-    </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J24" t="s">
+        <v>76</v>
+      </c>
+      <c r="K24">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A25">
-        <v>898.21749999999997</v>
+        <v>889.98086363636367</v>
       </c>
       <c r="B25">
-        <v>-83.440000000000055</v>
+        <v>-40.899999999999977</v>
       </c>
       <c r="C25" t="s">
-        <v>63</v>
+        <v>77</v>
       </c>
       <c r="D25" t="s">
-        <v>64</v>
+        <v>78</v>
       </c>
       <c r="E25">
+        <v>15</v>
+      </c>
+      <c r="F25">
+        <v>3</v>
+      </c>
+      <c r="G25">
+        <v>2</v>
+      </c>
+      <c r="H25">
+        <v>10</v>
+      </c>
+      <c r="J25" t="s">
+        <v>79</v>
+      </c>
+      <c r="K25">
+        <v>1.4</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A26">
+        <v>888.03750000000002</v>
+      </c>
+      <c r="B26">
+        <v>-93.62</v>
+      </c>
+      <c r="C26" t="s">
+        <v>80</v>
+      </c>
+      <c r="D26" t="s">
+        <v>81</v>
+      </c>
+      <c r="E26">
         <v>17</v>
       </c>
-      <c r="F25">
-        <v>3</v>
-      </c>
-      <c r="G25">
-        <v>3</v>
-      </c>
-      <c r="H25">
+      <c r="F26">
+        <v>3</v>
+      </c>
+      <c r="G26">
+        <v>3</v>
+      </c>
+      <c r="H26">
         <v>11</v>
       </c>
-    </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A26">
-        <v>891.85086363636367</v>
-      </c>
-      <c r="B26">
-        <v>-39.029999999999973</v>
-      </c>
-      <c r="C26" t="s">
-        <v>65</v>
-      </c>
-      <c r="D26" t="s">
-        <v>66</v>
-      </c>
-      <c r="E26">
-        <v>15</v>
-      </c>
-      <c r="F26">
-        <v>3</v>
-      </c>
-      <c r="G26">
-        <v>2</v>
-      </c>
-      <c r="H26">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J26" t="s">
+        <v>82</v>
+      </c>
+      <c r="K26">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A27">
-        <v>883.32400000000007</v>
+        <v>878.71400000000006</v>
       </c>
       <c r="B27">
-        <v>-50.899999999999977</v>
+        <v>-55.509999999999991</v>
       </c>
       <c r="C27" t="s">
-        <v>67</v>
+        <v>83</v>
       </c>
       <c r="D27" t="s">
-        <v>68</v>
+        <v>84</v>
       </c>
       <c r="E27">
         <v>39</v>
@@ -1480,19 +1615,25 @@
       <c r="H27">
         <v>23</v>
       </c>
-    </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J27" t="s">
+        <v>85</v>
+      </c>
+      <c r="K27">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A28">
-        <v>874.17086363636361</v>
+        <v>874.1808636363636</v>
       </c>
       <c r="B28">
-        <v>-56.710000000000036</v>
+        <v>-56.700000000000045</v>
       </c>
       <c r="C28" t="s">
-        <v>69</v>
+        <v>86</v>
       </c>
       <c r="D28" t="s">
-        <v>70</v>
+        <v>87</v>
       </c>
       <c r="E28">
         <v>15</v>
@@ -1507,18 +1648,18 @@
         <v>13</v>
       </c>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A29">
-        <v>852.85086363636367</v>
+        <v>847.97086363636367</v>
       </c>
       <c r="B29">
-        <v>-78.029999999999973</v>
+        <v>-82.909999999999968</v>
       </c>
       <c r="C29" t="s">
-        <v>71</v>
+        <v>88</v>
       </c>
       <c r="D29" t="s">
-        <v>72</v>
+        <v>89</v>
       </c>
       <c r="E29">
         <v>17</v>

--- a/Ranking_Data.xlsx
+++ b/Ranking_Data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="c:\Users\원영이\Desktop\ATL AUTO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B959A7CA-3F4C-476D-8D9B-ED98A4225228}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{283B688D-4A40-410D-B15C-2439A75D1127}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-114" yWindow="-114" windowWidth="36727" windowHeight="20317" xr2:uid="{77D11D44-0FCC-406F-A50A-69EA4B11D0A1}"/>
+    <workbookView xWindow="-114" yWindow="-114" windowWidth="36727" windowHeight="20317" xr2:uid="{0F401D83-4CF9-4BEA-833D-FCBB8E94DD21}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -95,57 +95,57 @@
     <t>경기 수</t>
   </si>
   <si>
+    <t>피파왕초보구단주</t>
+  </si>
+  <si>
+    <t>리버풀</t>
+  </si>
+  <si>
+    <t>3부리그</t>
+  </si>
+  <si>
+    <t>검정소</t>
+  </si>
+  <si>
+    <t>AC 밀란</t>
+  </si>
+  <si>
+    <t>FA컵</t>
+  </si>
+  <si>
     <t>UNIT</t>
   </si>
   <si>
     <t>AS 로마</t>
   </si>
   <si>
-    <t>3부리그</t>
-  </si>
-  <si>
-    <t>검정소</t>
-  </si>
-  <si>
-    <t>AC 밀란</t>
-  </si>
-  <si>
-    <t>FA컵</t>
-  </si>
-  <si>
-    <t>피파왕초보구단주</t>
-  </si>
-  <si>
-    <t>리버풀</t>
-  </si>
-  <si>
     <t>UEFA_D조</t>
   </si>
   <si>
+    <t>앙쿠</t>
+  </si>
+  <si>
+    <t>아틀레티코 마드리드</t>
+  </si>
+  <si>
+    <t>UEFA Tournament</t>
+  </si>
+  <si>
+    <t>콩콩콩룔</t>
+  </si>
+  <si>
+    <t>라치오</t>
+  </si>
+  <si>
+    <t>전체 합계</t>
+  </si>
+  <si>
     <t>방덕</t>
   </si>
   <si>
     <t>인테르</t>
   </si>
   <si>
-    <t>UEFA Tournament</t>
-  </si>
-  <si>
-    <t>앙쿠</t>
-  </si>
-  <si>
-    <t>아틀레티코 마드리드</t>
-  </si>
-  <si>
-    <t>전체 합계</t>
-  </si>
-  <si>
-    <t>콩콩콩룔</t>
-  </si>
-  <si>
-    <t>라치오</t>
-  </si>
-  <si>
     <t>은안</t>
   </si>
   <si>
@@ -164,27 +164,27 @@
     <t>2부리그</t>
   </si>
   <si>
+    <t>오스트리아</t>
+  </si>
+  <si>
+    <t>마인츠</t>
+  </si>
+  <si>
+    <t>0708ManUtd</t>
+  </si>
+  <si>
+    <t>레알 마드리드</t>
+  </si>
+  <si>
+    <t>FA컵_결승전</t>
+  </si>
+  <si>
     <t>Special블루</t>
   </si>
   <si>
     <t>아스널</t>
   </si>
   <si>
-    <t>오스트리아</t>
-  </si>
-  <si>
-    <t>마인츠</t>
-  </si>
-  <si>
-    <t>FA컵_결승전</t>
-  </si>
-  <si>
-    <t>0708ManUtd</t>
-  </si>
-  <si>
-    <t>레알 마드리드</t>
-  </si>
-  <si>
     <t>FA컵_4강</t>
   </si>
   <si>
@@ -254,21 +254,21 @@
     <t>UEL_FINAL</t>
   </si>
   <si>
+    <t>Gucci차붐</t>
+  </si>
+  <si>
+    <t>전북 현대 모터스</t>
+  </si>
+  <si>
+    <t>UEL_4강</t>
+  </si>
+  <si>
     <t>Legend독수리</t>
   </si>
   <si>
     <t>맨체스터 유나이티드</t>
   </si>
   <si>
-    <t>UEL_4강</t>
-  </si>
-  <si>
-    <t>Gucci차붐</t>
-  </si>
-  <si>
-    <t>전북 현대 모터스</t>
-  </si>
-  <si>
     <t>UEL_8강</t>
   </si>
   <si>
@@ -299,16 +299,16 @@
     <t>UECL_8강</t>
   </si>
   <si>
+    <t>겐지간지</t>
+  </si>
+  <si>
+    <t>파리 생제르맹</t>
+  </si>
+  <si>
     <t>ShangHaiPortFC</t>
   </si>
   <si>
     <t>상하이 선화</t>
-  </si>
-  <si>
-    <t>겐지간지</t>
-  </si>
-  <si>
-    <t>파리 생제르맹</t>
   </si>
 </sst>
 </file>
@@ -691,7 +691,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2E1CE71F-4539-4E45-9F4B-8330E79A9FA2}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A6D410C8-5870-4DAA-98A4-60E50A50AC7A}">
   <dimension ref="A1:O29"/>
   <sheetFormatPr defaultRowHeight="15.7" x14ac:dyDescent="0.3"/>
   <sheetData>
@@ -758,10 +758,10 @@
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A3">
-        <v>1215.144</v>
+        <v>1225.4840000000002</v>
       </c>
       <c r="B3">
-        <v>100.27999999999997</v>
+        <v>110.62000000000012</v>
       </c>
       <c r="C3" t="s">
         <v>13</v>
@@ -770,10 +770,10 @@
         <v>14</v>
       </c>
       <c r="E3">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F3">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G3">
         <v>2</v>
@@ -802,10 +802,10 @@
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A4">
-        <v>1122.4575</v>
+        <v>1170.3875</v>
       </c>
       <c r="B4">
-        <v>91.639999999999873</v>
+        <v>116.17000000000007</v>
       </c>
       <c r="C4" t="s">
         <v>18</v>
@@ -814,16 +814,16 @@
         <v>19</v>
       </c>
       <c r="E4">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="F4">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="G4">
+        <v>4</v>
+      </c>
+      <c r="H4">
         <v>5</v>
-      </c>
-      <c r="H4">
-        <v>7</v>
       </c>
       <c r="J4" t="s">
         <v>20</v>
@@ -846,10 +846,10 @@
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A5">
-        <v>1107.9375</v>
+        <v>1129.5374999999999</v>
       </c>
       <c r="B5">
-        <v>58.980000000000018</v>
+        <v>80.579999999999927</v>
       </c>
       <c r="C5" t="s">
         <v>21</v>
@@ -858,10 +858,10 @@
         <v>22</v>
       </c>
       <c r="E5">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F5">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G5">
         <v>2</v>
@@ -890,10 +890,10 @@
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A6">
-        <v>1098.4974999999999</v>
+        <v>1122.4575</v>
       </c>
       <c r="B6">
-        <v>44.279999999999973</v>
+        <v>91.639999999999873</v>
       </c>
       <c r="C6" t="s">
         <v>24</v>
@@ -902,16 +902,16 @@
         <v>25</v>
       </c>
       <c r="E6">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="F6">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="G6">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H6">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J6" t="s">
         <v>26</v>
@@ -934,10 +934,10 @@
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A7">
-        <v>1091.6190000000001</v>
+        <v>1090.4550000000002</v>
       </c>
       <c r="B7">
-        <v>64.75</v>
+        <v>97.870000000000118</v>
       </c>
       <c r="C7" t="s">
         <v>27</v>
@@ -946,16 +946,16 @@
         <v>28</v>
       </c>
       <c r="E7">
-        <v>21</v>
+        <v>40</v>
       </c>
       <c r="F7">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="G7">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="H7">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="J7" t="s">
         <v>29</v>
@@ -978,10 +978,10 @@
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A8">
-        <v>1090.4550000000002</v>
+        <v>1087.93</v>
       </c>
       <c r="B8">
-        <v>97.870000000000118</v>
+        <v>80.830000000000041</v>
       </c>
       <c r="C8" t="s">
         <v>30</v>
@@ -990,16 +990,16 @@
         <v>31</v>
       </c>
       <c r="E8">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="F8">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="G8">
+        <v>3</v>
+      </c>
+      <c r="H8">
         <v>10</v>
-      </c>
-      <c r="H8">
-        <v>4</v>
       </c>
       <c r="J8" t="s">
         <v>32</v>
@@ -1022,10 +1022,10 @@
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A9">
-        <v>1087.93</v>
+        <v>1064.7690000000002</v>
       </c>
       <c r="B9">
-        <v>80.830000000000041</v>
+        <v>37.900000000000091</v>
       </c>
       <c r="C9" t="s">
         <v>33</v>
@@ -1037,21 +1037,21 @@
         <v>23</v>
       </c>
       <c r="F9">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G9">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H9">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A10">
-        <v>1078.375</v>
+        <v>1050.875</v>
       </c>
       <c r="B10">
-        <v>34.210000000000036</v>
+        <v>6.7100000000000364</v>
       </c>
       <c r="C10" t="s">
         <v>35</v>
@@ -1060,7 +1060,7 @@
         <v>36</v>
       </c>
       <c r="E10">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="F10">
         <v>10</v>
@@ -1069,7 +1069,7 @@
         <v>3</v>
       </c>
       <c r="H10">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J10" t="s">
         <v>37</v>
@@ -1112,10 +1112,10 @@
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A12">
-        <v>1027.8825000000002</v>
+        <v>1017.1890000000002</v>
       </c>
       <c r="B12">
-        <v>-11.730000000000018</v>
+        <v>-23.330000000000041</v>
       </c>
       <c r="C12" t="s">
         <v>41</v>
@@ -1124,16 +1124,16 @@
         <v>42</v>
       </c>
       <c r="E12">
+        <v>39</v>
+      </c>
+      <c r="F12">
         <v>22</v>
       </c>
-      <c r="F12">
-        <v>11</v>
-      </c>
       <c r="G12">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="H12">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J12" t="s">
         <v>20</v>
@@ -1144,10 +1144,10 @@
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A13">
-        <v>1017.1890000000002</v>
+        <v>1016.3608636363637</v>
       </c>
       <c r="B13">
-        <v>-23.330000000000041</v>
+        <v>85.480000000000018</v>
       </c>
       <c r="C13" t="s">
         <v>43</v>
@@ -1156,16 +1156,16 @@
         <v>44</v>
       </c>
       <c r="E13">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="F13">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="G13">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="H13">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J13" t="s">
         <v>45</v>
@@ -1176,10 +1176,10 @@
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A14">
-        <v>1010.4208636363636</v>
+        <v>1010.3125000000002</v>
       </c>
       <c r="B14">
-        <v>79.539999999999964</v>
+        <v>-29.299999999999955</v>
       </c>
       <c r="C14" t="s">
         <v>46</v>
@@ -1188,16 +1188,16 @@
         <v>47</v>
       </c>
       <c r="E14">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F14">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G14">
         <v>4</v>
       </c>
       <c r="H14">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J14" t="s">
         <v>48</v>
@@ -1304,10 +1304,10 @@
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A18">
-        <v>993.9308636363636</v>
+        <v>981.12086363636365</v>
       </c>
       <c r="B18">
-        <v>63.049999999999955</v>
+        <v>50.240000000000009</v>
       </c>
       <c r="C18" t="s">
         <v>56</v>
@@ -1316,16 +1316,16 @@
         <v>57</v>
       </c>
       <c r="E18">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="F18">
         <v>12</v>
       </c>
       <c r="G18">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H18">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J18" t="s">
         <v>58</v>
@@ -1336,10 +1336,10 @@
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A19">
-        <v>970.77086363636363</v>
+        <v>980.97086363636367</v>
       </c>
       <c r="B19">
-        <v>39.889999999999986</v>
+        <v>50.090000000000032</v>
       </c>
       <c r="C19" t="s">
         <v>59</v>
@@ -1348,22 +1348,22 @@
         <v>60</v>
       </c>
       <c r="E19">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="F19">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="G19">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H19">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="J19" t="s">
         <v>61</v>
       </c>
       <c r="K19">
-        <v>2.2999999999999998</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.3">
@@ -1395,7 +1395,7 @@
         <v>64</v>
       </c>
       <c r="K20">
-        <v>2</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.3">
@@ -1427,7 +1427,7 @@
         <v>67</v>
       </c>
       <c r="K21">
-        <v>1.7</v>
+        <v>1.9</v>
       </c>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.3">
@@ -1459,15 +1459,15 @@
         <v>70</v>
       </c>
       <c r="K22">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A23">
-        <v>914.75400000000002</v>
+        <v>924.21749999999997</v>
       </c>
       <c r="B23">
-        <v>-19.470000000000027</v>
+        <v>-57.440000000000055</v>
       </c>
       <c r="C23" t="s">
         <v>71</v>
@@ -1476,16 +1476,16 @@
         <v>72</v>
       </c>
       <c r="E23">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="F23">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="G23">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H23">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="J23" t="s">
         <v>73</v>
@@ -1496,10 +1496,10 @@
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A24">
-        <v>901.28750000000002</v>
+        <v>914.75400000000002</v>
       </c>
       <c r="B24">
-        <v>-80.37</v>
+        <v>-19.470000000000027</v>
       </c>
       <c r="C24" t="s">
         <v>74</v>
@@ -1508,16 +1508,16 @@
         <v>75</v>
       </c>
       <c r="E24">
+        <v>40</v>
+      </c>
+      <c r="F24">
+        <v>11</v>
+      </c>
+      <c r="G24">
+        <v>6</v>
+      </c>
+      <c r="H24">
         <v>23</v>
-      </c>
-      <c r="F24">
-        <v>5</v>
-      </c>
-      <c r="G24">
-        <v>4</v>
-      </c>
-      <c r="H24">
-        <v>14</v>
       </c>
       <c r="J24" t="s">
         <v>76</v>
@@ -1555,15 +1555,15 @@
         <v>79</v>
       </c>
       <c r="K25">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A26">
-        <v>895.39086363636363</v>
+        <v>893.73086363636367</v>
       </c>
       <c r="B26">
-        <v>-35.490000000000009</v>
+        <v>-37.149999999999977</v>
       </c>
       <c r="C26" t="s">
         <v>80</v>
@@ -1572,16 +1572,16 @@
         <v>81</v>
       </c>
       <c r="E26">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="F26">
         <v>8</v>
       </c>
       <c r="G26">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H26">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J26" t="s">
         <v>82</v>
@@ -1592,10 +1592,10 @@
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A27">
-        <v>858.45086363636358</v>
+        <v>885.92086363636361</v>
       </c>
       <c r="B27">
-        <v>-72.430000000000064</v>
+        <v>-44.960000000000036</v>
       </c>
       <c r="C27" t="s">
         <v>83</v>
@@ -1604,10 +1604,10 @@
         <v>84</v>
       </c>
       <c r="E27">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="F27">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G27">
         <v>5</v>
@@ -1624,10 +1624,10 @@
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A28">
-        <v>842.88086363636364</v>
+        <v>796.29086363636361</v>
       </c>
       <c r="B28">
-        <v>-88</v>
+        <v>-134.59000000000003</v>
       </c>
       <c r="C28" t="s">
         <v>86</v>
@@ -1636,24 +1636,24 @@
         <v>87</v>
       </c>
       <c r="E28">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="F28">
         <v>4</v>
       </c>
       <c r="G28">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H28">
-        <v>23</v>
+        <v>27</v>
       </c>
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A29">
-        <v>796.29086363636361</v>
+        <v>792.37086363636365</v>
       </c>
       <c r="B29">
-        <v>-134.59000000000003</v>
+        <v>-138.51</v>
       </c>
       <c r="C29" t="s">
         <v>88</v>
@@ -1662,16 +1662,16 @@
         <v>89</v>
       </c>
       <c r="E29">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="F29">
         <v>4</v>
       </c>
       <c r="G29">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H29">
-        <v>27</v>
+        <v>30</v>
       </c>
     </row>
   </sheetData>

--- a/Ranking_Data.xlsx
+++ b/Ranking_Data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="c:\Users\원영이\Desktop\ATL AUTO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{283B688D-4A40-410D-B15C-2439A75D1127}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{3C1B34DC-0CA3-49A3-942B-12B8466E6052}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-114" yWindow="-114" windowWidth="36727" windowHeight="20317" xr2:uid="{0F401D83-4CF9-4BEA-833D-FCBB8E94DD21}"/>
+    <workbookView xWindow="-114" yWindow="-114" windowWidth="36727" windowHeight="20317" xr2:uid="{E07F4BE3-A0F3-4333-889C-AC3A7DD5F563}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -164,19 +164,28 @@
     <t>2부리그</t>
   </si>
   <si>
+    <t>호야국2인</t>
+  </si>
+  <si>
+    <t>SSC 나폴리</t>
+  </si>
+  <si>
     <t>오스트리아</t>
   </si>
   <si>
     <t>마인츠</t>
   </si>
   <si>
+    <t>FA컵_결승전</t>
+  </si>
+  <si>
     <t>0708ManUtd</t>
   </si>
   <si>
     <t>레알 마드리드</t>
   </si>
   <si>
-    <t>FA컵_결승전</t>
+    <t>FA컵_4강</t>
   </si>
   <si>
     <t>Special블루</t>
@@ -185,18 +194,9 @@
     <t>아스널</t>
   </si>
   <si>
-    <t>FA컵_4강</t>
-  </si>
-  <si>
     <t>FA컵_8강</t>
   </si>
   <si>
-    <t>호야국2인</t>
-  </si>
-  <si>
-    <t>SSC 나폴리</t>
-  </si>
-  <si>
     <t>FA컵_16강</t>
   </si>
   <si>
@@ -281,34 +281,34 @@
     <t>UECL_FINAL</t>
   </si>
   <si>
+    <t>A지냐크</t>
+  </si>
+  <si>
+    <t>올랭피크 마르세유</t>
+  </si>
+  <si>
+    <t>UECL_4강</t>
+  </si>
+  <si>
     <t>syma</t>
   </si>
   <si>
     <t>RC 셀타 비고</t>
   </si>
   <si>
-    <t>UECL_4강</t>
-  </si>
-  <si>
-    <t>A지냐크</t>
-  </si>
-  <si>
-    <t>올랭피크 마르세유</t>
-  </si>
-  <si>
     <t>UECL_8강</t>
   </si>
   <si>
+    <t>ShangHaiPortFC</t>
+  </si>
+  <si>
+    <t>상하이 선화</t>
+  </si>
+  <si>
     <t>겐지간지</t>
   </si>
   <si>
     <t>파리 생제르맹</t>
-  </si>
-  <si>
-    <t>ShangHaiPortFC</t>
-  </si>
-  <si>
-    <t>상하이 선화</t>
   </si>
 </sst>
 </file>
@@ -691,7 +691,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A6D410C8-5870-4DAA-98A4-60E50A50AC7A}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8B425FF5-5CBA-48E4-B51A-B53B50B91855}">
   <dimension ref="A1:O29"/>
   <sheetFormatPr defaultRowHeight="15.7" x14ac:dyDescent="0.3"/>
   <sheetData>
@@ -802,10 +802,10 @@
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A4">
-        <v>1170.3875</v>
+        <v>1158.1975</v>
       </c>
       <c r="B4">
-        <v>116.17000000000007</v>
+        <v>103.98000000000002</v>
       </c>
       <c r="C4" t="s">
         <v>18</v>
@@ -814,16 +814,16 @@
         <v>19</v>
       </c>
       <c r="E4">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="F4">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G4">
         <v>4</v>
       </c>
       <c r="H4">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J4" t="s">
         <v>20</v>
@@ -1112,10 +1112,10 @@
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A12">
-        <v>1017.1890000000002</v>
+        <v>1019.654</v>
       </c>
       <c r="B12">
-        <v>-23.330000000000041</v>
+        <v>17.819999999999936</v>
       </c>
       <c r="C12" t="s">
         <v>41</v>
@@ -1124,13 +1124,13 @@
         <v>42</v>
       </c>
       <c r="E12">
-        <v>39</v>
+        <v>25</v>
       </c>
       <c r="F12">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="G12">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="H12">
         <v>10</v>
@@ -1144,10 +1144,10 @@
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A13">
-        <v>1016.3608636363637</v>
+        <v>1017.1890000000002</v>
       </c>
       <c r="B13">
-        <v>85.480000000000018</v>
+        <v>-23.330000000000041</v>
       </c>
       <c r="C13" t="s">
         <v>43</v>
@@ -1156,16 +1156,16 @@
         <v>44</v>
       </c>
       <c r="E13">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="F13">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="G13">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H13">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J13" t="s">
         <v>45</v>
@@ -1176,10 +1176,10 @@
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A14">
-        <v>1010.3125000000002</v>
+        <v>1016.3608636363637</v>
       </c>
       <c r="B14">
-        <v>-29.299999999999955</v>
+        <v>85.480000000000018</v>
       </c>
       <c r="C14" t="s">
         <v>46</v>
@@ -1188,16 +1188,16 @@
         <v>47</v>
       </c>
       <c r="E14">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="F14">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="G14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H14">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J14" t="s">
         <v>48</v>
@@ -1208,31 +1208,31 @@
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A15">
-        <v>1009.0708636363636</v>
+        <v>1010.3125000000002</v>
       </c>
       <c r="B15">
-        <v>78.189999999999941</v>
+        <v>-29.299999999999955</v>
       </c>
       <c r="C15" t="s">
+        <v>49</v>
+      </c>
+      <c r="D15" t="s">
+        <v>50</v>
+      </c>
+      <c r="E15">
+        <v>26</v>
+      </c>
+      <c r="F15">
+        <v>12</v>
+      </c>
+      <c r="G15">
+        <v>4</v>
+      </c>
+      <c r="H15">
         <v>10</v>
       </c>
-      <c r="D15" t="s">
-        <v>12</v>
-      </c>
-      <c r="E15">
-        <v>40</v>
-      </c>
-      <c r="F15">
-        <v>22</v>
-      </c>
-      <c r="G15">
-        <v>5</v>
-      </c>
-      <c r="H15">
-        <v>13</v>
-      </c>
       <c r="J15" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="K15">
         <v>1.7</v>
@@ -1240,28 +1240,28 @@
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A16">
-        <v>1007.904</v>
+        <v>1009.0708636363636</v>
       </c>
       <c r="B16">
-        <v>6.0699999999999363</v>
+        <v>78.189999999999941</v>
       </c>
       <c r="C16" t="s">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="D16" t="s">
-        <v>51</v>
+        <v>12</v>
       </c>
       <c r="E16">
-        <v>23</v>
+        <v>40</v>
       </c>
       <c r="F16">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="G16">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H16">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="J16" t="s">
         <v>52</v>
@@ -1304,10 +1304,10 @@
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A18">
-        <v>981.12086363636365</v>
+        <v>1003.7208636363637</v>
       </c>
       <c r="B18">
-        <v>50.240000000000009</v>
+        <v>72.840000000000032</v>
       </c>
       <c r="C18" t="s">
         <v>56</v>
@@ -1316,10 +1316,10 @@
         <v>57</v>
       </c>
       <c r="E18">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="F18">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="G18">
         <v>7</v>
@@ -1560,10 +1560,10 @@
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A26">
-        <v>893.73086363636367</v>
+        <v>885.92086363636361</v>
       </c>
       <c r="B26">
-        <v>-37.149999999999977</v>
+        <v>-44.960000000000036</v>
       </c>
       <c r="C26" t="s">
         <v>80</v>
@@ -1575,13 +1575,13 @@
         <v>33</v>
       </c>
       <c r="F26">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G26">
         <v>5</v>
       </c>
       <c r="H26">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="J26" t="s">
         <v>82</v>
@@ -1592,10 +1592,10 @@
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A27">
-        <v>885.92086363636361</v>
+        <v>882.4408636363637</v>
       </c>
       <c r="B27">
-        <v>-44.960000000000036</v>
+        <v>-48.439999999999941</v>
       </c>
       <c r="C27" t="s">
         <v>83</v>
@@ -1604,16 +1604,16 @@
         <v>84</v>
       </c>
       <c r="E27">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F27">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G27">
         <v>5</v>
       </c>
       <c r="H27">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J27" t="s">
         <v>85</v>
@@ -1624,10 +1624,10 @@
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A28">
-        <v>796.29086363636361</v>
+        <v>792.37086363636365</v>
       </c>
       <c r="B28">
-        <v>-134.59000000000003</v>
+        <v>-138.51</v>
       </c>
       <c r="C28" t="s">
         <v>86</v>
@@ -1636,24 +1636,24 @@
         <v>87</v>
       </c>
       <c r="E28">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="F28">
         <v>4</v>
       </c>
       <c r="G28">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H28">
-        <v>27</v>
+        <v>30</v>
       </c>
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A29">
-        <v>792.37086363636365</v>
+        <v>791.83086363636357</v>
       </c>
       <c r="B29">
-        <v>-138.51</v>
+        <v>-139.05000000000007</v>
       </c>
       <c r="C29" t="s">
         <v>88</v>
@@ -1662,16 +1662,16 @@
         <v>89</v>
       </c>
       <c r="E29">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="F29">
         <v>4</v>
       </c>
       <c r="G29">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H29">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
   </sheetData>

--- a/Ranking_Data.xlsx
+++ b/Ranking_Data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="c:\Users\원영이\Desktop\ATL AUTO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{3B66CCA1-0C39-470B-A8B1-A0AEAA8DDEAB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{CEA34473-D72B-463E-A045-97CF6DF77FF2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-114" yWindow="-114" windowWidth="36727" windowHeight="20317" xr2:uid="{44BBE9A8-27F5-4C92-B22D-67FBE6433A83}"/>
+    <workbookView xWindow="399" yWindow="713" windowWidth="32621" windowHeight="17608" xr2:uid="{FA52CCD2-948F-48C4-B640-3223512B602E}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -65,85 +65,112 @@
     <t>패</t>
   </si>
   <si>
+    <t>개포동덕배</t>
+  </si>
+  <si>
+    <t>바이에른 뮌헨</t>
+  </si>
+  <si>
+    <t>UNIT</t>
+  </si>
+  <si>
+    <t>17시즌</t>
+  </si>
+  <si>
+    <t>AS 로마</t>
+  </si>
+  <si>
+    <t>검정소</t>
+  </si>
+  <si>
+    <t>AC 밀란</t>
+  </si>
+  <si>
+    <t>대회종류</t>
+  </si>
+  <si>
+    <t>ELO 변동값</t>
+  </si>
+  <si>
+    <t>경기 수</t>
+  </si>
+  <si>
     <t>Voor</t>
   </si>
   <si>
     <t>첼시</t>
   </si>
   <si>
-    <t>UNIT</t>
-  </si>
-  <si>
-    <t>17시즌</t>
-  </si>
-  <si>
-    <t>AS 로마</t>
-  </si>
-  <si>
-    <t>개포동덕배</t>
-  </si>
-  <si>
-    <t>바이에른 뮌헨</t>
-  </si>
-  <si>
-    <t>대회종류</t>
-  </si>
-  <si>
-    <t>ELO 변동값</t>
-  </si>
-  <si>
-    <t>경기 수</t>
-  </si>
-  <si>
     <t>1부리그</t>
   </si>
   <si>
-    <t>검정소</t>
-  </si>
-  <si>
-    <t>AC 밀란</t>
-  </si>
-  <si>
     <t>FA컵</t>
   </si>
   <si>
+    <t>ZD장인지참치</t>
+  </si>
+  <si>
+    <t>레버쿠젠</t>
+  </si>
+  <si>
+    <t>UEFA_A조</t>
+  </si>
+  <si>
+    <t>피파왕초보구단주</t>
+  </si>
+  <si>
+    <t>리버풀</t>
+  </si>
+  <si>
+    <t>UCL</t>
+  </si>
+  <si>
+    <t>콩콩콩룔</t>
+  </si>
+  <si>
+    <t>라치오</t>
+  </si>
+  <si>
+    <t>전체 합계</t>
+  </si>
+  <si>
+    <t>방덕</t>
+  </si>
+  <si>
+    <t>인테르</t>
+  </si>
+  <si>
+    <t>셀래스틴</t>
+  </si>
+  <si>
+    <t>바르셀로나</t>
+  </si>
+  <si>
     <t>앙쿠</t>
   </si>
   <si>
     <t>아틀레티코 마드리드</t>
   </si>
   <si>
-    <t>UEFA_A조</t>
-  </si>
-  <si>
-    <t>피파왕초보구단주</t>
-  </si>
-  <si>
-    <t>리버풀</t>
-  </si>
-  <si>
-    <t>UCL</t>
-  </si>
-  <si>
-    <t>콩콩콩룔</t>
-  </si>
-  <si>
-    <t>라치오</t>
-  </si>
-  <si>
-    <t>전체 합계</t>
-  </si>
-  <si>
-    <t>방덕</t>
-  </si>
-  <si>
-    <t>인테르</t>
-  </si>
-  <si>
-    <t>셀래스틴</t>
-  </si>
-  <si>
-    <t>바르셀로나</t>
+    <t>2부리그</t>
+  </si>
+  <si>
+    <t>호야국2인</t>
+  </si>
+  <si>
+    <t>SSC 나폴리</t>
+  </si>
+  <si>
+    <t>3부리그</t>
+  </si>
+  <si>
+    <t>Special블루</t>
+  </si>
+  <si>
+    <t>아스널</t>
+  </si>
+  <si>
+    <t>FA컵_결승전</t>
   </si>
   <si>
     <t>은안</t>
@@ -152,33 +179,6 @@
     <t>맨체스터 시티</t>
   </si>
   <si>
-    <t>2부리그</t>
-  </si>
-  <si>
-    <t>Special블루</t>
-  </si>
-  <si>
-    <t>아스널</t>
-  </si>
-  <si>
-    <t>3부리그</t>
-  </si>
-  <si>
-    <t>ZD장인지참치</t>
-  </si>
-  <si>
-    <t>레버쿠젠</t>
-  </si>
-  <si>
-    <t>FA컵_결승전</t>
-  </si>
-  <si>
-    <t>호야국2인</t>
-  </si>
-  <si>
-    <t>SSC 나폴리</t>
-  </si>
-  <si>
     <t>FA컵_4강</t>
   </si>
   <si>
@@ -209,28 +209,28 @@
     <t>FA컵_32강</t>
   </si>
   <si>
+    <t>비주류중독</t>
+  </si>
+  <si>
+    <t>셀틱 FC</t>
+  </si>
+  <si>
+    <t>UEFA</t>
+  </si>
+  <si>
     <t>용신</t>
   </si>
   <si>
     <t>토트넘</t>
   </si>
   <si>
-    <t>UEFA</t>
+    <t>UCL_결승전</t>
   </si>
   <si>
     <t>Gucci차붐</t>
   </si>
   <si>
     <t>전북 현대 모터스</t>
-  </si>
-  <si>
-    <t>UCL_결승전</t>
-  </si>
-  <si>
-    <t>비주류중독</t>
-  </si>
-  <si>
-    <t>셀틱 FC</t>
   </si>
   <si>
     <t>UCL_4강</t>
@@ -691,7 +691,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{94C59142-3C0E-4C00-8B28-A146F60040FC}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{796F12D2-ACD8-4CC4-B9D2-F1381838E237}">
   <dimension ref="A1:O29"/>
   <sheetFormatPr defaultRowHeight="15.7" x14ac:dyDescent="0.3"/>
   <sheetData>
@@ -723,10 +723,10 @@
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A2">
-        <v>1257.28</v>
+        <v>1307.7962500000001</v>
       </c>
       <c r="B2">
-        <v>122.5</v>
+        <v>171.67000000000007</v>
       </c>
       <c r="C2" t="s">
         <v>8</v>
@@ -738,13 +738,13 @@
         <v>29</v>
       </c>
       <c r="F2">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="G2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H2">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="J2" t="s">
         <v>10</v>
@@ -758,10 +758,10 @@
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A3">
-        <v>1250.0862500000001</v>
+        <v>1273.4100000000001</v>
       </c>
       <c r="B3">
-        <v>113.96000000000004</v>
+        <v>215.94000000000005</v>
       </c>
       <c r="C3" t="s">
         <v>13</v>
@@ -770,16 +770,16 @@
         <v>14</v>
       </c>
       <c r="E3">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F3">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="G3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H3">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="J3" t="s">
         <v>15</v>
@@ -802,31 +802,31 @@
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A4">
-        <v>1231.9599999999998</v>
+        <v>1257.8</v>
       </c>
       <c r="B4">
-        <v>193.15999999999985</v>
+        <v>123.01999999999998</v>
       </c>
       <c r="C4" t="s">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="D4" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E4">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F4">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="G4">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H4">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J4" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="K4">
         <v>31.680000000000007</v>
@@ -846,40 +846,40 @@
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A5">
-        <v>1182.94</v>
+        <v>1247.6299999999999</v>
       </c>
       <c r="B5">
-        <v>125.47000000000003</v>
+        <v>208.82999999999993</v>
       </c>
       <c r="C5" t="s">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="D5" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="E5">
-        <v>19</v>
+        <v>35</v>
       </c>
       <c r="F5">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="G5">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="H5">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="J5" t="s">
         <v>21</v>
       </c>
       <c r="K5">
-        <v>39.82</v>
+        <v>57.83</v>
       </c>
       <c r="L5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N5">
         <v>0</v>
@@ -890,10 +890,10 @@
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A6">
-        <v>1124.5225</v>
+        <v>1135.4090000000001</v>
       </c>
       <c r="B6">
-        <v>123.90000000000009</v>
+        <v>195.74</v>
       </c>
       <c r="C6" t="s">
         <v>22</v>
@@ -902,16 +902,16 @@
         <v>23</v>
       </c>
       <c r="E6">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="F6">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G6">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="H6">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="J6" t="s">
         <v>24</v>
@@ -961,19 +961,19 @@
         <v>27</v>
       </c>
       <c r="K7">
-        <v>83.78</v>
+        <v>81.44</v>
       </c>
       <c r="L7">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="M7">
+        <v>3</v>
+      </c>
+      <c r="N7">
         <v>2</v>
       </c>
-      <c r="N7">
-        <v>1</v>
-      </c>
       <c r="O7">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.3">
@@ -1005,19 +1005,19 @@
         <v>30</v>
       </c>
       <c r="K8">
-        <v>193.16</v>
+        <v>208.83</v>
       </c>
       <c r="L8">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="M8">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="N8">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O8">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.3">
@@ -1048,10 +1048,10 @@
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A10">
-        <v>1077.739</v>
+        <v>1093.259</v>
       </c>
       <c r="B10">
-        <v>138.06999999999994</v>
+        <v>153.58999999999992</v>
       </c>
       <c r="C10" t="s">
         <v>33</v>
@@ -1060,19 +1060,19 @@
         <v>34</v>
       </c>
       <c r="E10">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="F10">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="G10">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="H10">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="J10" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="K10">
         <v>2</v>
@@ -1080,10 +1080,10 @@
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A11">
-        <v>1060.29</v>
+        <v>1093.0425</v>
       </c>
       <c r="B11">
-        <v>9.9100000000000819</v>
+        <v>92.420000000000073</v>
       </c>
       <c r="C11" t="s">
         <v>35</v>
@@ -1092,16 +1092,16 @@
         <v>36</v>
       </c>
       <c r="E11">
-        <v>21</v>
+        <v>45</v>
       </c>
       <c r="F11">
+        <v>28</v>
+      </c>
+      <c r="G11">
         <v>10</v>
       </c>
-      <c r="G11">
-        <v>3</v>
-      </c>
       <c r="H11">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J11" t="s">
         <v>37</v>
@@ -1112,10 +1112,10 @@
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A12">
-        <v>1049.76</v>
+        <v>1060.77125</v>
       </c>
       <c r="B12">
-        <v>-4.5699999999999363</v>
+        <v>30.5</v>
       </c>
       <c r="C12" t="s">
         <v>38</v>
@@ -1124,16 +1124,16 @@
         <v>39</v>
       </c>
       <c r="E12">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="F12">
         <v>14</v>
       </c>
       <c r="G12">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H12">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="J12" t="s">
         <v>40</v>
@@ -1144,10 +1144,10 @@
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A13">
-        <v>1037.1590000000001</v>
+        <v>1049.76</v>
       </c>
       <c r="B13">
-        <v>97.490000000000009</v>
+        <v>-4.5699999999999363</v>
       </c>
       <c r="C13" t="s">
         <v>41</v>
@@ -1156,16 +1156,16 @@
         <v>42</v>
       </c>
       <c r="E13">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="F13">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="G13">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H13">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="J13" t="s">
         <v>43</v>
@@ -1176,10 +1176,10 @@
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A14">
-        <v>1035.58125</v>
+        <v>1045.9299999999998</v>
       </c>
       <c r="B14">
-        <v>5.3099999999999454</v>
+        <v>-4.4500000000000455</v>
       </c>
       <c r="C14" t="s">
         <v>44</v>
@@ -1188,16 +1188,16 @@
         <v>45</v>
       </c>
       <c r="E14">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="F14">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="G14">
         <v>3</v>
       </c>
       <c r="H14">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="J14" t="s">
         <v>46</v>
@@ -1270,7 +1270,7 @@
         <v>1.6</v>
       </c>
     </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>1030.3562499999998</v>
       </c>
@@ -1302,12 +1302,12 @@
         <v>1.4</v>
       </c>
     </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A18">
-        <v>997.39900000000011</v>
+        <v>987.35900000000015</v>
       </c>
       <c r="B18">
-        <v>57.730000000000018</v>
+        <v>47.690000000000055</v>
       </c>
       <c r="C18" t="s">
         <v>56</v>
@@ -1316,13 +1316,13 @@
         <v>57</v>
       </c>
       <c r="E18">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="F18">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G18">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H18">
         <v>13</v>
@@ -1334,12 +1334,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A19">
-        <v>997.17500000000007</v>
+        <v>980.00900000000013</v>
       </c>
       <c r="B19">
-        <v>10.200000000000045</v>
+        <v>40.340000000000032</v>
       </c>
       <c r="C19" t="s">
         <v>59</v>
@@ -1348,13 +1348,13 @@
         <v>60</v>
       </c>
       <c r="E19">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="F19">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="G19">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H19">
         <v>15</v>
@@ -1366,12 +1366,12 @@
         <v>2.5</v>
       </c>
     </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A20">
-        <v>987.35900000000015</v>
+        <v>975.125</v>
       </c>
       <c r="B20">
-        <v>47.690000000000055</v>
+        <v>-11.850000000000023</v>
       </c>
       <c r="C20" t="s">
         <v>62</v>
@@ -1380,16 +1380,16 @@
         <v>63</v>
       </c>
       <c r="E20">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F20">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="G20">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H20">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="J20" t="s">
         <v>64</v>
@@ -1398,12 +1398,12 @@
         <v>2.2000000000000002</v>
       </c>
     </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A21">
-        <v>980.19124999999985</v>
+        <v>970.53124999999989</v>
       </c>
       <c r="B21">
-        <v>21.559999999999945</v>
+        <v>11.899999999999977</v>
       </c>
       <c r="C21" t="s">
         <v>65</v>
@@ -1412,16 +1412,16 @@
         <v>66</v>
       </c>
       <c r="E21">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="F21">
         <v>16</v>
       </c>
       <c r="G21">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H21">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="J21" t="s">
         <v>67</v>
@@ -1430,7 +1430,7 @@
         <v>1.9</v>
       </c>
     </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>954.3599999999999</v>
       </c>
@@ -1462,7 +1462,7 @@
         <v>1.9</v>
       </c>
     </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>944.05900000000008</v>
       </c>
@@ -1494,7 +1494,7 @@
         <v>1.6</v>
       </c>
     </row>
-    <row r="24" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>924.23124999999993</v>
       </c>
@@ -1526,7 +1526,7 @@
         <v>1.4</v>
       </c>
     </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>906.21900000000005</v>
       </c>
@@ -1557,14 +1557,8 @@
       <c r="K25">
         <v>1.5</v>
       </c>
-      <c r="N25">
-        <v>13.47</v>
-      </c>
-      <c r="O25">
-        <v>19.690000000000001</v>
-      </c>
-    </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.3">
+    </row>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>895.80900000000008</v>
       </c>
@@ -1595,19 +1589,13 @@
       <c r="K26">
         <v>1.4</v>
       </c>
-      <c r="N26">
-        <v>12.28</v>
-      </c>
-      <c r="O26">
-        <v>17.52</v>
-      </c>
-    </row>
-    <row r="27" spans="1:15" x14ac:dyDescent="0.3">
+    </row>
+    <row r="27" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A27">
-        <v>878.24900000000014</v>
+        <v>885.59900000000016</v>
       </c>
       <c r="B27">
-        <v>-61.419999999999959</v>
+        <v>-54.069999999999936</v>
       </c>
       <c r="C27" t="s">
         <v>83</v>
@@ -1616,13 +1604,13 @@
         <v>84</v>
       </c>
       <c r="E27">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="F27">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G27">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H27">
         <v>23</v>
@@ -1634,7 +1622,7 @@
         <v>1.3</v>
       </c>
     </row>
-    <row r="28" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>803.15900000000011</v>
       </c>
@@ -1660,7 +1648,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="29" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>791.43900000000008</v>
       </c>

--- a/Ranking_Data.xlsx
+++ b/Ranking_Data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="c:\Users\원영이\Desktop\ATL AUTO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{ABD2CC6C-8572-4E53-8627-B1E4317C37A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{1838F154-D4D6-4109-AB27-388C4E5B4C42}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="399" yWindow="713" windowWidth="32621" windowHeight="17608" xr2:uid="{15A1EBFA-6923-488A-9059-3FED25C20F40}"/>
+    <workbookView xWindow="1084" yWindow="1397" windowWidth="32621" windowHeight="17608" xr2:uid="{3070C2AF-2AB3-4AE3-8697-3B720F2B6226}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -71,39 +71,39 @@
     <t>바이에른 뮌헨</t>
   </si>
   <si>
+    <t>검정소</t>
+  </si>
+  <si>
+    <t>17시즌</t>
+  </si>
+  <si>
+    <t>AC 밀란</t>
+  </si>
+  <si>
+    <t>대회종류</t>
+  </si>
+  <si>
+    <t>ELO 변동값</t>
+  </si>
+  <si>
+    <t>경기 수</t>
+  </si>
+  <si>
+    <t>Voor</t>
+  </si>
+  <si>
+    <t>첼시</t>
+  </si>
+  <si>
+    <t>1부리그</t>
+  </si>
+  <si>
     <t>UNIT</t>
   </si>
   <si>
-    <t>17시즌</t>
-  </si>
-  <si>
     <t>AS 로마</t>
   </si>
   <si>
-    <t>검정소</t>
-  </si>
-  <si>
-    <t>AC 밀란</t>
-  </si>
-  <si>
-    <t>대회종류</t>
-  </si>
-  <si>
-    <t>ELO 변동값</t>
-  </si>
-  <si>
-    <t>경기 수</t>
-  </si>
-  <si>
-    <t>Voor</t>
-  </si>
-  <si>
-    <t>첼시</t>
-  </si>
-  <si>
-    <t>1부리그</t>
-  </si>
-  <si>
     <t>FA컵</t>
   </si>
   <si>
@@ -113,7 +113,16 @@
     <t>레버쿠젠</t>
   </si>
   <si>
-    <t>UEFA_A조</t>
+    <t>UEFA_B조</t>
+  </si>
+  <si>
+    <t>셀래스틴</t>
+  </si>
+  <si>
+    <t>바르셀로나</t>
+  </si>
+  <si>
+    <t>UCL</t>
   </si>
   <si>
     <t>피파왕초보구단주</t>
@@ -122,7 +131,7 @@
     <t>리버풀</t>
   </si>
   <si>
-    <t>UCL</t>
+    <t>전체 합계</t>
   </si>
   <si>
     <t>콩콩콩룔</t>
@@ -131,19 +140,10 @@
     <t>라치오</t>
   </si>
   <si>
-    <t>전체 합계</t>
-  </si>
-  <si>
     <t>방덕</t>
   </si>
   <si>
     <t>인테르</t>
-  </si>
-  <si>
-    <t>셀래스틴</t>
-  </si>
-  <si>
-    <t>바르셀로나</t>
   </si>
   <si>
     <t>앙쿠</t>
@@ -691,7 +691,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CDECBEC3-E0B8-413C-925B-05FB41CF9922}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0E737F7B-E491-4A89-B6B7-38C3530AC328}">
   <dimension ref="A1:O29"/>
   <sheetFormatPr defaultRowHeight="15.7" x14ac:dyDescent="0.3"/>
   <sheetData>
@@ -758,37 +758,37 @@
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A3">
-        <v>1273.4100000000001</v>
+        <v>1282.19</v>
       </c>
       <c r="B3">
-        <v>215.94000000000005</v>
+        <v>224.72000000000003</v>
       </c>
       <c r="C3" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="D3" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E3">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F3">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H3">
         <v>6</v>
       </c>
       <c r="J3" t="s">
+        <v>13</v>
+      </c>
+      <c r="K3" t="s">
+        <v>14</v>
+      </c>
+      <c r="L3" t="s">
         <v>15</v>
-      </c>
-      <c r="K3" t="s">
-        <v>16</v>
-      </c>
-      <c r="L3" t="s">
-        <v>17</v>
       </c>
       <c r="M3" t="s">
         <v>5</v>
@@ -808,10 +808,10 @@
         <v>123.01999999999998</v>
       </c>
       <c r="C4" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D4" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E4">
         <v>32</v>
@@ -826,22 +826,22 @@
         <v>9</v>
       </c>
       <c r="J4" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="K4">
-        <v>31.680000000000007</v>
+        <v>58.65</v>
       </c>
       <c r="L4">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="M4">
         <v>4</v>
       </c>
       <c r="N4">
+        <v>1</v>
+      </c>
+      <c r="O4">
         <v>3</v>
-      </c>
-      <c r="O4">
-        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.3">
@@ -852,10 +852,10 @@
         <v>208.82999999999993</v>
       </c>
       <c r="C5" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="D5" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="E5">
         <v>35</v>
@@ -873,27 +873,27 @@
         <v>21</v>
       </c>
       <c r="K5">
-        <v>57.83</v>
+        <v>-23.09</v>
       </c>
       <c r="L5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N5">
         <v>0</v>
       </c>
       <c r="O5">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A6">
-        <v>1135.4090000000001</v>
+        <v>1180.6090000000002</v>
       </c>
       <c r="B6">
-        <v>195.74</v>
+        <v>240.94000000000005</v>
       </c>
       <c r="C6" t="s">
         <v>22</v>
@@ -902,42 +902,42 @@
         <v>23</v>
       </c>
       <c r="E6">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="F6">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="G6">
         <v>5</v>
       </c>
       <c r="H6">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="J6" t="s">
         <v>24</v>
       </c>
       <c r="K6">
-        <v>37.880000000000003</v>
+        <v>80.97</v>
       </c>
       <c r="L6">
         <v>12</v>
       </c>
       <c r="M6">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="N6">
         <v>2</v>
       </c>
       <c r="O6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A7">
-        <v>1115.9450000000002</v>
+        <v>1123.2690000000002</v>
       </c>
       <c r="B7">
-        <v>50.940000000000055</v>
+        <v>183.60000000000014</v>
       </c>
       <c r="C7" t="s">
         <v>25</v>
@@ -946,42 +946,42 @@
         <v>26</v>
       </c>
       <c r="E7">
-        <v>25</v>
+        <v>48</v>
       </c>
       <c r="F7">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="G7">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="H7">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="J7" t="s">
         <v>27</v>
       </c>
       <c r="K7">
-        <v>81.44</v>
+        <v>108.19</v>
       </c>
       <c r="L7">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="M7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O7">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A8">
-        <v>1098.1475</v>
+        <v>1115.9450000000002</v>
       </c>
       <c r="B8">
-        <v>81.300000000000068</v>
+        <v>50.940000000000055</v>
       </c>
       <c r="C8" t="s">
         <v>28</v>
@@ -990,42 +990,42 @@
         <v>29</v>
       </c>
       <c r="E8">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="F8">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G8">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H8">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J8" t="s">
         <v>30</v>
       </c>
       <c r="K8">
-        <v>208.83</v>
+        <v>224.72</v>
       </c>
       <c r="L8">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="M8">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="N8">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="O8">
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A9">
-        <v>1095.0862499999998</v>
+        <v>1106.2774999999999</v>
       </c>
       <c r="B9">
-        <v>61.769999999999982</v>
+        <v>89.42999999999995</v>
       </c>
       <c r="C9" t="s">
         <v>31</v>
@@ -1034,24 +1034,24 @@
         <v>32</v>
       </c>
       <c r="E9">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F9">
         <v>10</v>
       </c>
       <c r="G9">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H9">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A10">
-        <v>1093.259</v>
+        <v>1095.0862499999998</v>
       </c>
       <c r="B10">
-        <v>153.58999999999992</v>
+        <v>61.769999999999982</v>
       </c>
       <c r="C10" t="s">
         <v>33</v>
@@ -1060,19 +1060,19 @@
         <v>34</v>
       </c>
       <c r="E10">
-        <v>43</v>
+        <v>26</v>
       </c>
       <c r="F10">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="G10">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="H10">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J10" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="K10">
         <v>2</v>
@@ -1336,10 +1336,10 @@
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A19">
-        <v>980.00900000000013</v>
+        <v>986.87900000000013</v>
       </c>
       <c r="B19">
-        <v>40.340000000000032</v>
+        <v>47.210000000000036</v>
       </c>
       <c r="C19" t="s">
         <v>59</v>
@@ -1348,10 +1348,10 @@
         <v>60</v>
       </c>
       <c r="E19">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="F19">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="G19">
         <v>6</v>
@@ -1592,10 +1592,10 @@
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A27">
-        <v>885.59900000000016</v>
+        <v>878.62900000000013</v>
       </c>
       <c r="B27">
-        <v>-54.069999999999936</v>
+        <v>-61.039999999999964</v>
       </c>
       <c r="C27" t="s">
         <v>83</v>
@@ -1604,7 +1604,7 @@
         <v>84</v>
       </c>
       <c r="E27">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F27">
         <v>10</v>
@@ -1613,7 +1613,7 @@
         <v>7</v>
       </c>
       <c r="H27">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="J27" t="s">
         <v>85</v>

--- a/Ranking_Data.xlsx
+++ b/Ranking_Data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="c:\Users\원영이\Desktop\ATL AUTO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{1838F154-D4D6-4109-AB27-388C4E5B4C42}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{543DE379-C0DF-4FE1-BFB2-86821631417E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1084" yWindow="1397" windowWidth="32621" windowHeight="17608" xr2:uid="{3070C2AF-2AB3-4AE3-8697-3B720F2B6226}"/>
+    <workbookView xWindow="1084" yWindow="1397" windowWidth="32621" windowHeight="17608" xr2:uid="{59E2070D-6FDE-429B-ADCD-4F6032C2705F}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -691,7 +691,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0E737F7B-E491-4A89-B6B7-38C3530AC328}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{502A9930-7F1F-4F32-8E8B-DDA591DFEA1B}">
   <dimension ref="A1:O29"/>
   <sheetFormatPr defaultRowHeight="15.7" x14ac:dyDescent="0.3"/>
   <sheetData>
@@ -1400,10 +1400,10 @@
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A21">
-        <v>970.53124999999989</v>
+        <v>969.67124999999987</v>
       </c>
       <c r="B21">
-        <v>11.899999999999977</v>
+        <v>11.039999999999964</v>
       </c>
       <c r="C21" t="s">
         <v>65</v>
@@ -1412,16 +1412,16 @@
         <v>66</v>
       </c>
       <c r="E21">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="F21">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G21">
         <v>5</v>
       </c>
       <c r="H21">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J21" t="s">
         <v>67</v>
@@ -1464,10 +1464,10 @@
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A23">
-        <v>944.05900000000008</v>
+        <v>944.89900000000011</v>
       </c>
       <c r="B23">
-        <v>4.3899999999999864</v>
+        <v>5.2300000000000182</v>
       </c>
       <c r="C23" t="s">
         <v>71</v>
@@ -1476,16 +1476,16 @@
         <v>72</v>
       </c>
       <c r="E23">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="F23">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G23">
         <v>3</v>
       </c>
       <c r="H23">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J23" t="s">
         <v>73</v>

--- a/Ranking_Data.xlsx
+++ b/Ranking_Data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="c:\Users\원영이\Desktop\ATL AUTO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{3EFEE5E0-2575-4F46-AE03-B6AACA6806B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{220126F8-60E9-4B73-BE88-1D2EC0F220F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1768" yWindow="2082" windowWidth="32621" windowHeight="17608" xr2:uid="{9676FA2C-4EB3-4B76-AA59-6F1E23D3AFD2}"/>
+    <workbookView xWindow="1768" yWindow="2082" windowWidth="32621" windowHeight="17608" xr2:uid="{FBE25928-4B1C-472D-A332-8AB790EDD3DD}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -691,7 +691,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{99B4FFAB-8F37-46E9-8E6C-762D6515ECE3}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D63FD46F-5F57-4600-B694-F043849C44AC}">
   <dimension ref="A1:O29"/>
   <sheetFormatPr defaultRowHeight="15.7" x14ac:dyDescent="0.3"/>
   <sheetData>

--- a/Ranking_Data.xlsx
+++ b/Ranking_Data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="c:\Users\원영이\Desktop\ATL AUTO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{220126F8-60E9-4B73-BE88-1D2EC0F220F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{813DA5A0-B6BB-481F-A21A-E69F37B430D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1768" yWindow="2082" windowWidth="32621" windowHeight="17608" xr2:uid="{FBE25928-4B1C-472D-A332-8AB790EDD3DD}"/>
+    <workbookView xWindow="356" yWindow="356" windowWidth="27346" windowHeight="14928" xr2:uid="{BD68F837-4A2D-445D-8E00-A03B39CC34B3}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -691,7 +691,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D63FD46F-5F57-4600-B694-F043849C44AC}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EE5715B8-2D1B-47A9-9C2B-7F6756B04028}">
   <dimension ref="A1:O29"/>
   <sheetFormatPr defaultRowHeight="15.7" x14ac:dyDescent="0.3"/>
   <sheetData>

--- a/Ranking_Data.xlsx
+++ b/Ranking_Data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="c:\Users\원영이\Desktop\ATL AUTO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D8549F57-1C77-4EF7-B3D3-56EB0927AF79}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{CF13DED5-9476-4A4D-91DB-FDC1D629C09F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-114" yWindow="-114" windowWidth="36727" windowHeight="20317" xr2:uid="{4BC53C65-DFDC-44D7-859D-6D6B67016694}"/>
+    <workbookView xWindow="1682" yWindow="1654" windowWidth="27731" windowHeight="17394" xr2:uid="{4BB37996-E190-46DF-BF1C-FCCF79CC5FCF}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -134,34 +134,43 @@
     <t>전체 합계</t>
   </si>
   <si>
+    <t>0708ManUtd</t>
+  </si>
+  <si>
+    <t>레알 마드리드</t>
+  </si>
+  <si>
+    <t>방덕</t>
+  </si>
+  <si>
+    <t>인테르</t>
+  </si>
+  <si>
+    <t>앙쿠</t>
+  </si>
+  <si>
+    <t>아틀레티코 마드리드</t>
+  </si>
+  <si>
+    <t>2부리그</t>
+  </si>
+  <si>
+    <t>은안</t>
+  </si>
+  <si>
+    <t>맨체스터 시티</t>
+  </si>
+  <si>
+    <t>3부리그</t>
+  </si>
+  <si>
     <t>콩콩콩룔</t>
   </si>
   <si>
     <t>라치오</t>
   </si>
   <si>
-    <t>방덕</t>
-  </si>
-  <si>
-    <t>인테르</t>
-  </si>
-  <si>
-    <t>앙쿠</t>
-  </si>
-  <si>
-    <t>아틀레티코 마드리드</t>
-  </si>
-  <si>
-    <t>2부리그</t>
-  </si>
-  <si>
-    <t>은안</t>
-  </si>
-  <si>
-    <t>맨체스터 시티</t>
-  </si>
-  <si>
-    <t>3부리그</t>
+    <t>FA컵_결승전</t>
   </si>
   <si>
     <t>호야국2인</t>
@@ -170,7 +179,7 @@
     <t>SSC 나폴리</t>
   </si>
   <si>
-    <t>FA컵_결승전</t>
+    <t>FA컵_4강</t>
   </si>
   <si>
     <t>오스트리아</t>
@@ -179,7 +188,7 @@
     <t>마인츠</t>
   </si>
   <si>
-    <t>FA컵_4강</t>
+    <t>FA컵_8강</t>
   </si>
   <si>
     <t>Special블루</t>
@@ -188,7 +197,7 @@
     <t>아스널</t>
   </si>
   <si>
-    <t>FA컵_8강</t>
+    <t>FA컵_16강</t>
   </si>
   <si>
     <t>아들러</t>
@@ -197,15 +206,6 @@
     <t>프랑크푸르트</t>
   </si>
   <si>
-    <t>FA컵_16강</t>
-  </si>
-  <si>
-    <t>0708ManUtd</t>
-  </si>
-  <si>
-    <t>레알 마드리드</t>
-  </si>
-  <si>
     <t>FA컵_32강</t>
   </si>
   <si>
@@ -236,21 +236,21 @@
     <t>UCL_4강</t>
   </si>
   <si>
+    <t>Gucci와퍼</t>
+  </si>
+  <si>
+    <t>함부르크SV</t>
+  </si>
+  <si>
+    <t>UCL_8강</t>
+  </si>
+  <si>
     <t>경남FC가즈아</t>
   </si>
   <si>
     <t>경남 FC</t>
   </si>
   <si>
-    <t>UCL_8강</t>
-  </si>
-  <si>
-    <t>Gucci와퍼</t>
-  </si>
-  <si>
-    <t>함부르크SV</t>
-  </si>
-  <si>
     <t>UEL_FINAL</t>
   </si>
   <si>
@@ -272,19 +272,19 @@
     <t>UEL_8강</t>
   </si>
   <si>
+    <t>suma수마</t>
+  </si>
+  <si>
+    <t>ACF 피오렌티나</t>
+  </si>
+  <si>
+    <t>UECL_FINAL</t>
+  </si>
+  <si>
     <t>A지냐크</t>
   </si>
   <si>
     <t>올랭피크 마르세유</t>
-  </si>
-  <si>
-    <t>UECL_FINAL</t>
-  </si>
-  <si>
-    <t>suma수마</t>
-  </si>
-  <si>
-    <t>ACF 피오렌티나</t>
   </si>
   <si>
     <t>UECL_4강</t>
@@ -691,7 +691,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{200DCEA8-5AE5-46EE-AFAA-32B988C5E55D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F1CF9C09-4342-4DCB-86DC-8483EE765F37}">
   <dimension ref="A1:O29"/>
   <sheetFormatPr defaultRowHeight="15.7" x14ac:dyDescent="0.3"/>
   <sheetData>
@@ -758,10 +758,10 @@
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A3">
-        <v>1274.8400000000001</v>
+        <v>1293.1500000000001</v>
       </c>
       <c r="B3">
-        <v>217.37000000000012</v>
+        <v>235.68000000000006</v>
       </c>
       <c r="C3" t="s">
         <v>10</v>
@@ -770,10 +770,10 @@
         <v>12</v>
       </c>
       <c r="E3">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F3">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G3">
         <v>4</v>
@@ -829,13 +829,13 @@
         <v>18</v>
       </c>
       <c r="K4">
-        <v>51.3</v>
+        <v>69.61</v>
       </c>
       <c r="L4">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="M4">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N4">
         <v>1</v>
@@ -1005,13 +1005,13 @@
         <v>30</v>
       </c>
       <c r="K8">
-        <v>217.37</v>
+        <v>235.68</v>
       </c>
       <c r="L8">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="M8">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="N8">
         <v>4</v>
@@ -1022,10 +1022,10 @@
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A9">
-        <v>1106.2774999999999</v>
+        <v>1105.739</v>
       </c>
       <c r="B9">
-        <v>89.42999999999995</v>
+        <v>166.06999999999994</v>
       </c>
       <c r="C9" t="s">
         <v>31</v>
@@ -1034,13 +1034,13 @@
         <v>32</v>
       </c>
       <c r="E9">
-        <v>25</v>
+        <v>41</v>
       </c>
       <c r="F9">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="G9">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H9">
         <v>11</v>
@@ -1144,10 +1144,10 @@
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A13">
-        <v>1060.77125</v>
+        <v>1073.0374999999999</v>
       </c>
       <c r="B13">
-        <v>30.5</v>
+        <v>56.189999999999941</v>
       </c>
       <c r="C13" t="s">
         <v>41</v>
@@ -1156,13 +1156,13 @@
         <v>42</v>
       </c>
       <c r="E13">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="F13">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="G13">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H13">
         <v>13</v>
@@ -1176,10 +1176,10 @@
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A14">
-        <v>1056.4762499999999</v>
+        <v>1060.77125</v>
       </c>
       <c r="B14">
-        <v>-2.1099999999999</v>
+        <v>30.5</v>
       </c>
       <c r="C14" t="s">
         <v>44</v>
@@ -1188,16 +1188,16 @@
         <v>45</v>
       </c>
       <c r="E14">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="F14">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="G14">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="H14">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="J14" t="s">
         <v>46</v>
@@ -1208,10 +1208,10 @@
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A15">
-        <v>1049.76</v>
+        <v>1056.4762499999999</v>
       </c>
       <c r="B15">
-        <v>-4.5699999999999363</v>
+        <v>-2.1099999999999</v>
       </c>
       <c r="C15" t="s">
         <v>47</v>
@@ -1220,13 +1220,13 @@
         <v>48</v>
       </c>
       <c r="E15">
-        <v>28</v>
+        <v>41</v>
       </c>
       <c r="F15">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="G15">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="H15">
         <v>10</v>
@@ -1240,10 +1240,10 @@
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A16">
-        <v>1031.8049999999998</v>
+        <v>1049.76</v>
       </c>
       <c r="B16">
-        <v>-14.120000000000118</v>
+        <v>-4.5699999999999363</v>
       </c>
       <c r="C16" t="s">
         <v>50</v>
@@ -1255,13 +1255,13 @@
         <v>28</v>
       </c>
       <c r="F16">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G16">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H16">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="J16" t="s">
         <v>52</v>
@@ -1272,10 +1272,10 @@
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A17">
-        <v>1030.809</v>
+        <v>1031.8049999999998</v>
       </c>
       <c r="B17">
-        <v>91.139999999999873</v>
+        <v>-14.120000000000118</v>
       </c>
       <c r="C17" t="s">
         <v>53</v>
@@ -1284,16 +1284,16 @@
         <v>54</v>
       </c>
       <c r="E17">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="F17">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="G17">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H17">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="J17" t="s">
         <v>55</v>
@@ -1336,10 +1336,10 @@
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A19">
-        <v>982.26900000000012</v>
+        <v>980.69900000000007</v>
       </c>
       <c r="B19">
-        <v>42.600000000000023</v>
+        <v>41.029999999999973</v>
       </c>
       <c r="C19" t="s">
         <v>59</v>
@@ -1348,16 +1348,16 @@
         <v>60</v>
       </c>
       <c r="E19">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F19">
         <v>18</v>
       </c>
       <c r="G19">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H19">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J19" t="s">
         <v>61</v>
@@ -1400,10 +1400,10 @@
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A21">
-        <v>969.67124999999987</v>
+        <v>972.31999999999994</v>
       </c>
       <c r="B21">
-        <v>11.039999999999964</v>
+        <v>-10.009999999999991</v>
       </c>
       <c r="C21" t="s">
         <v>65</v>
@@ -1412,16 +1412,16 @@
         <v>66</v>
       </c>
       <c r="E21">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="F21">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="G21">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H21">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="J21" t="s">
         <v>67</v>
@@ -1432,10 +1432,10 @@
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A22">
-        <v>954.3599999999999</v>
+        <v>969.67124999999987</v>
       </c>
       <c r="B22">
-        <v>-27.970000000000027</v>
+        <v>11.039999999999964</v>
       </c>
       <c r="C22" t="s">
         <v>68</v>
@@ -1444,16 +1444,16 @@
         <v>69</v>
       </c>
       <c r="E22">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="F22">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="G22">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H22">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="J22" t="s">
         <v>70</v>
@@ -1528,10 +1528,10 @@
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A25">
-        <v>889.33900000000006</v>
+        <v>887.14900000000011</v>
       </c>
       <c r="B25">
-        <v>-50.330000000000041</v>
+        <v>-52.519999999999982</v>
       </c>
       <c r="C25" t="s">
         <v>77</v>
@@ -1540,16 +1540,16 @@
         <v>78</v>
       </c>
       <c r="E25">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="F25">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="G25">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H25">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="J25" t="s">
         <v>79</v>
@@ -1560,10 +1560,10 @@
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A26">
-        <v>887.14900000000011</v>
+        <v>881.87900000000013</v>
       </c>
       <c r="B26">
-        <v>-52.519999999999982</v>
+        <v>-57.789999999999964</v>
       </c>
       <c r="C26" t="s">
         <v>80</v>
@@ -1572,16 +1572,16 @@
         <v>81</v>
       </c>
       <c r="E26">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F26">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="G26">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H26">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="J26" t="s">
         <v>82</v>

--- a/Ranking_Data.xlsx
+++ b/Ranking_Data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="c:\Users\원영이\Desktop\ATL AUTO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{DFE19ABA-1B83-4735-BFF3-7BC89C54A325}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{52223723-A456-414C-BF8D-800D685C31C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1682" yWindow="1654" windowWidth="27731" windowHeight="17394" xr2:uid="{81ADA542-DD6E-448B-A562-CA57ACBE94F6}"/>
+    <workbookView xWindow="2025" yWindow="1996" windowWidth="27730" windowHeight="17394" xr2:uid="{54557B03-EE8B-47A7-87C5-407FDEEBFCCD}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -65,21 +65,27 @@
     <t>패</t>
   </si>
   <si>
+    <t>검정소</t>
+  </si>
+  <si>
+    <t>AC 밀란</t>
+  </si>
+  <si>
+    <t>셀래스틴</t>
+  </si>
+  <si>
+    <t>17시즌</t>
+  </si>
+  <si>
+    <t>바르셀로나</t>
+  </si>
+  <si>
     <t>개포동덕배</t>
   </si>
   <si>
     <t>바이에른 뮌헨</t>
   </si>
   <si>
-    <t>검정소</t>
-  </si>
-  <si>
-    <t>17시즌</t>
-  </si>
-  <si>
-    <t>AC 밀란</t>
-  </si>
-  <si>
     <t>대회종류</t>
   </si>
   <si>
@@ -95,34 +101,94 @@
     <t>첼시</t>
   </si>
   <si>
+    <t>3부리그</t>
+  </si>
+  <si>
+    <t>UNIT</t>
+  </si>
+  <si>
+    <t>AS 로마</t>
+  </si>
+  <si>
+    <t>FA컵</t>
+  </si>
+  <si>
+    <t>ZD장인지참치</t>
+  </si>
+  <si>
+    <t>레버쿠젠</t>
+  </si>
+  <si>
+    <t>UEFA_A조</t>
+  </si>
+  <si>
+    <t>UEL</t>
+  </si>
+  <si>
+    <t>0708ManUtd</t>
+  </si>
+  <si>
+    <t>레알 마드리드</t>
+  </si>
+  <si>
+    <t>전체 합계</t>
+  </si>
+  <si>
+    <t>앙쿠</t>
+  </si>
+  <si>
+    <t>아틀레티코 마드리드</t>
+  </si>
+  <si>
+    <t>호야국2인</t>
+  </si>
+  <si>
+    <t>SSC 나폴리</t>
+  </si>
+  <si>
     <t>1부리그</t>
   </si>
   <si>
-    <t>UNIT</t>
-  </si>
-  <si>
-    <t>AS 로마</t>
-  </si>
-  <si>
-    <t>FA컵</t>
-  </si>
-  <si>
-    <t>ZD장인지참치</t>
-  </si>
-  <si>
-    <t>레버쿠젠</t>
-  </si>
-  <si>
-    <t>UEFA_B조</t>
-  </si>
-  <si>
-    <t>셀래스틴</t>
-  </si>
-  <si>
-    <t>바르셀로나</t>
-  </si>
-  <si>
-    <t>UCL</t>
+    <t>오스트리아</t>
+  </si>
+  <si>
+    <t>마인츠</t>
+  </si>
+  <si>
+    <t>2부리그</t>
+  </si>
+  <si>
+    <t>Special블루</t>
+  </si>
+  <si>
+    <t>아스널</t>
+  </si>
+  <si>
+    <t>콩콩콩룔</t>
+  </si>
+  <si>
+    <t>라치오</t>
+  </si>
+  <si>
+    <t>FA컵_결승전</t>
+  </si>
+  <si>
+    <t>아들러</t>
+  </si>
+  <si>
+    <t>프랑크푸르트</t>
+  </si>
+  <si>
+    <t>FA컵_4강</t>
+  </si>
+  <si>
+    <t>비주류중독</t>
+  </si>
+  <si>
+    <t>셀틱 FC</t>
+  </si>
+  <si>
+    <t>FA컵_8강</t>
   </si>
   <si>
     <t>피파왕초보구단주</t>
@@ -131,13 +197,7 @@
     <t>리버풀</t>
   </si>
   <si>
-    <t>전체 합계</t>
-  </si>
-  <si>
-    <t>0708ManUtd</t>
-  </si>
-  <si>
-    <t>레알 마드리드</t>
+    <t>FA컵_16강</t>
   </si>
   <si>
     <t>방덕</t>
@@ -146,13 +206,7 @@
     <t>인테르</t>
   </si>
   <si>
-    <t>앙쿠</t>
-  </si>
-  <si>
-    <t>아틀레티코 마드리드</t>
-  </si>
-  <si>
-    <t>2부리그</t>
+    <t>FA컵_32강</t>
   </si>
   <si>
     <t>은안</t>
@@ -161,60 +215,6 @@
     <t>맨체스터 시티</t>
   </si>
   <si>
-    <t>3부리그</t>
-  </si>
-  <si>
-    <t>콩콩콩룔</t>
-  </si>
-  <si>
-    <t>라치오</t>
-  </si>
-  <si>
-    <t>FA컵_결승전</t>
-  </si>
-  <si>
-    <t>호야국2인</t>
-  </si>
-  <si>
-    <t>SSC 나폴리</t>
-  </si>
-  <si>
-    <t>FA컵_4강</t>
-  </si>
-  <si>
-    <t>오스트리아</t>
-  </si>
-  <si>
-    <t>마인츠</t>
-  </si>
-  <si>
-    <t>FA컵_8강</t>
-  </si>
-  <si>
-    <t>Special블루</t>
-  </si>
-  <si>
-    <t>아스널</t>
-  </si>
-  <si>
-    <t>FA컵_16강</t>
-  </si>
-  <si>
-    <t>아들러</t>
-  </si>
-  <si>
-    <t>프랑크푸르트</t>
-  </si>
-  <si>
-    <t>FA컵_32강</t>
-  </si>
-  <si>
-    <t>비주류중독</t>
-  </si>
-  <si>
-    <t>셀틱 FC</t>
-  </si>
-  <si>
     <t>UEFA</t>
   </si>
   <si>
@@ -254,46 +254,46 @@
     <t>UEL_FINAL</t>
   </si>
   <si>
+    <t>Legend독수리</t>
+  </si>
+  <si>
+    <t>맨체스터 유나이티드</t>
+  </si>
+  <si>
+    <t>UEL_4강</t>
+  </si>
+  <si>
+    <t>suma수마</t>
+  </si>
+  <si>
+    <t>ACF 피오렌티나</t>
+  </si>
+  <si>
+    <t>UEL_8강</t>
+  </si>
+  <si>
+    <t>A지냐크</t>
+  </si>
+  <si>
+    <t>올랭피크 마르세유</t>
+  </si>
+  <si>
+    <t>UECL_FINAL</t>
+  </si>
+  <si>
+    <t>syma</t>
+  </si>
+  <si>
+    <t>RC 셀타 비고</t>
+  </si>
+  <si>
+    <t>UECL_4강</t>
+  </si>
+  <si>
     <t>여수가스</t>
   </si>
   <si>
     <t>AS 모나코</t>
-  </si>
-  <si>
-    <t>UEL_4강</t>
-  </si>
-  <si>
-    <t>Legend독수리</t>
-  </si>
-  <si>
-    <t>맨체스터 유나이티드</t>
-  </si>
-  <si>
-    <t>UEL_8강</t>
-  </si>
-  <si>
-    <t>suma수마</t>
-  </si>
-  <si>
-    <t>ACF 피오렌티나</t>
-  </si>
-  <si>
-    <t>UECL_FINAL</t>
-  </si>
-  <si>
-    <t>A지냐크</t>
-  </si>
-  <si>
-    <t>올랭피크 마르세유</t>
-  </si>
-  <si>
-    <t>UECL_4강</t>
-  </si>
-  <si>
-    <t>syma</t>
-  </si>
-  <si>
-    <t>RC 셀타 비고</t>
   </si>
   <si>
     <t>UECL_8강</t>
@@ -691,7 +691,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8A4DD104-89F7-466C-807F-25871C27FB15}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AB793AB5-7805-4470-A678-526A90488609}">
   <dimension ref="A1:O29"/>
   <sheetFormatPr defaultRowHeight="15.7" x14ac:dyDescent="0.3"/>
   <sheetData>
@@ -723,10 +723,10 @@
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A2">
-        <v>1307.7962500000001</v>
+        <v>1309.51</v>
       </c>
       <c r="B2">
-        <v>171.67000000000007</v>
+        <v>252.03999999999996</v>
       </c>
       <c r="C2" t="s">
         <v>8</v>
@@ -735,16 +735,16 @@
         <v>9</v>
       </c>
       <c r="E2">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F2">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="G2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H2">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="J2" t="s">
         <v>10</v>
@@ -758,37 +758,37 @@
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A3">
-        <v>1293.1500000000001</v>
+        <v>1307.7962500000001</v>
       </c>
       <c r="B3">
-        <v>235.68000000000006</v>
+        <v>171.67000000000007</v>
       </c>
       <c r="C3" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="D3" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E3">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F3">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="G3">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H3">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="J3" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="K3" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="L3" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="M3" t="s">
         <v>5</v>
@@ -808,10 +808,10 @@
         <v>123.01999999999998</v>
       </c>
       <c r="C4" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D4" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E4">
         <v>32</v>
@@ -826,22 +826,22 @@
         <v>9</v>
       </c>
       <c r="J4" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="K4">
-        <v>69.61</v>
+        <v>1.629999999999999</v>
       </c>
       <c r="L4">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="M4">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="N4">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="O4">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.3">
@@ -852,10 +852,10 @@
         <v>208.82999999999993</v>
       </c>
       <c r="C5" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D5" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="E5">
         <v>35</v>
@@ -870,19 +870,19 @@
         <v>10</v>
       </c>
       <c r="J5" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="K5">
-        <v>-23.09</v>
+        <v>43.269999999999996</v>
       </c>
       <c r="L5">
+        <v>4</v>
+      </c>
+      <c r="M5">
+        <v>2</v>
+      </c>
+      <c r="N5">
         <v>1</v>
-      </c>
-      <c r="M5">
-        <v>0</v>
-      </c>
-      <c r="N5">
-        <v>0</v>
       </c>
       <c r="O5">
         <v>1</v>
@@ -896,10 +896,10 @@
         <v>240.94000000000005</v>
       </c>
       <c r="C6" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="E6">
         <v>51</v>
@@ -914,22 +914,22 @@
         <v>16</v>
       </c>
       <c r="J6" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="K6">
-        <v>80.97</v>
+        <v>35.20000000000001</v>
       </c>
       <c r="L6">
         <v>12</v>
       </c>
       <c r="M6">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="N6">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O6">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.3">
@@ -940,10 +940,10 @@
         <v>182.97000000000003</v>
       </c>
       <c r="C7" t="s">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="D7" t="s">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="E7">
         <v>52</v>
@@ -961,27 +961,27 @@
         <v>27</v>
       </c>
       <c r="K7">
-        <v>108.19</v>
+        <v>102.87</v>
       </c>
       <c r="L7">
+        <v>10</v>
+      </c>
+      <c r="M7">
         <v>6</v>
       </c>
-      <c r="M7">
+      <c r="N7">
+        <v>0</v>
+      </c>
+      <c r="O7">
         <v>4</v>
-      </c>
-      <c r="N7">
-        <v>1</v>
-      </c>
-      <c r="O7">
-        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A8">
-        <v>1115.9450000000002</v>
+        <v>1105.739</v>
       </c>
       <c r="B8">
-        <v>50.940000000000055</v>
+        <v>166.06999999999994</v>
       </c>
       <c r="C8" t="s">
         <v>28</v>
@@ -990,42 +990,42 @@
         <v>29</v>
       </c>
       <c r="E8">
-        <v>25</v>
+        <v>41</v>
       </c>
       <c r="F8">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="G8">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H8">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="J8" t="s">
         <v>30</v>
       </c>
       <c r="K8">
-        <v>235.68</v>
+        <v>182.97</v>
       </c>
       <c r="L8">
-        <v>30</v>
+        <v>52</v>
       </c>
       <c r="M8">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="N8">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="O8">
-        <v>7</v>
+        <v>17</v>
       </c>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A9">
-        <v>1105.739</v>
+        <v>1093.0425</v>
       </c>
       <c r="B9">
-        <v>166.06999999999994</v>
+        <v>92.420000000000073</v>
       </c>
       <c r="C9" t="s">
         <v>31</v>
@@ -1034,24 +1034,24 @@
         <v>32</v>
       </c>
       <c r="E9">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="F9">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="G9">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="H9">
-        <v>11</v>
+        <v>7</v>
       </c>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A10">
-        <v>1095.0862499999998</v>
+        <v>1060.77125</v>
       </c>
       <c r="B10">
-        <v>61.769999999999982</v>
+        <v>30.5</v>
       </c>
       <c r="C10" t="s">
         <v>33</v>
@@ -1060,19 +1060,19 @@
         <v>34</v>
       </c>
       <c r="E10">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="F10">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="G10">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H10">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="J10" t="s">
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="K10">
         <v>2</v>
@@ -1080,31 +1080,31 @@
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A11">
-        <v>1093.0425</v>
+        <v>1056.4762499999999</v>
       </c>
       <c r="B11">
-        <v>92.420000000000073</v>
+        <v>-2.1099999999999</v>
       </c>
       <c r="C11" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D11" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E11">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="F11">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="G11">
+        <v>7</v>
+      </c>
+      <c r="H11">
         <v>10</v>
       </c>
-      <c r="H11">
-        <v>7</v>
-      </c>
       <c r="J11" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="K11">
         <v>1</v>
@@ -1112,31 +1112,31 @@
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A12">
-        <v>1086.8699999999999</v>
+        <v>1049.76</v>
       </c>
       <c r="B12">
-        <v>36.490000000000009</v>
+        <v>-4.5699999999999363</v>
       </c>
       <c r="C12" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D12" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E12">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="F12">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="G12">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H12">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J12" t="s">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="K12">
         <v>0.3</v>
@@ -1144,10 +1144,10 @@
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A13">
-        <v>1073.0374999999999</v>
+        <v>1036.7275</v>
       </c>
       <c r="B13">
-        <v>56.189999999999941</v>
+        <v>19.879999999999995</v>
       </c>
       <c r="C13" t="s">
         <v>41</v>
@@ -1156,7 +1156,7 @@
         <v>42</v>
       </c>
       <c r="E13">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F13">
         <v>10</v>
@@ -1165,7 +1165,7 @@
         <v>4</v>
       </c>
       <c r="H13">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="J13" t="s">
         <v>43</v>
@@ -1176,10 +1176,10 @@
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A14">
-        <v>1060.77125</v>
+        <v>1031.8049999999998</v>
       </c>
       <c r="B14">
-        <v>30.5</v>
+        <v>-14.120000000000118</v>
       </c>
       <c r="C14" t="s">
         <v>44</v>
@@ -1188,16 +1188,16 @@
         <v>45</v>
       </c>
       <c r="E14">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="F14">
+        <v>13</v>
+      </c>
+      <c r="G14">
+        <v>1</v>
+      </c>
+      <c r="H14">
         <v>14</v>
-      </c>
-      <c r="G14">
-        <v>3</v>
-      </c>
-      <c r="H14">
-        <v>13</v>
       </c>
       <c r="J14" t="s">
         <v>46</v>
@@ -1208,10 +1208,10 @@
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A15">
-        <v>1056.4762499999999</v>
+        <v>1025.3690000000001</v>
       </c>
       <c r="B15">
-        <v>-2.1099999999999</v>
+        <v>85.700000000000045</v>
       </c>
       <c r="C15" t="s">
         <v>47</v>
@@ -1220,16 +1220,16 @@
         <v>48</v>
       </c>
       <c r="E15">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="F15">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="G15">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="H15">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="J15" t="s">
         <v>49</v>
@@ -1240,10 +1240,10 @@
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A16">
-        <v>1049.76</v>
+        <v>999.84500000000014</v>
       </c>
       <c r="B16">
-        <v>-4.5699999999999363</v>
+        <v>-65.159999999999968</v>
       </c>
       <c r="C16" t="s">
         <v>50</v>
@@ -1252,16 +1252,16 @@
         <v>51</v>
       </c>
       <c r="E16">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F16">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G16">
         <v>4</v>
       </c>
       <c r="H16">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="J16" t="s">
         <v>52</v>
@@ -1272,10 +1272,10 @@
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A17">
-        <v>1031.8049999999998</v>
+        <v>995.08624999999984</v>
       </c>
       <c r="B17">
-        <v>-14.120000000000118</v>
+        <v>-38.230000000000018</v>
       </c>
       <c r="C17" t="s">
         <v>53</v>
@@ -1287,13 +1287,13 @@
         <v>28</v>
       </c>
       <c r="F17">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="G17">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H17">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="J17" t="s">
         <v>55</v>
@@ -1304,10 +1304,10 @@
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A18">
-        <v>987.35900000000015</v>
+        <v>986.86999999999989</v>
       </c>
       <c r="B18">
-        <v>47.690000000000055</v>
+        <v>-63.509999999999991</v>
       </c>
       <c r="C18" t="s">
         <v>56</v>
@@ -1316,13 +1316,13 @@
         <v>57</v>
       </c>
       <c r="E18">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="F18">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G18">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H18">
         <v>13</v>
@@ -1464,10 +1464,10 @@
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A23">
-        <v>949.52900000000011</v>
+        <v>924.23124999999993</v>
       </c>
       <c r="B23">
-        <v>9.8600000000000136</v>
+        <v>-21.210000000000036</v>
       </c>
       <c r="C23" t="s">
         <v>71</v>
@@ -1476,16 +1476,16 @@
         <v>72</v>
       </c>
       <c r="E23">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F23">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="G23">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H23">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="J23" t="s">
         <v>73</v>
@@ -1496,10 +1496,10 @@
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A24">
-        <v>924.23124999999993</v>
+        <v>887.14900000000011</v>
       </c>
       <c r="B24">
-        <v>-21.210000000000036</v>
+        <v>-52.519999999999982</v>
       </c>
       <c r="C24" t="s">
         <v>74</v>
@@ -1511,13 +1511,13 @@
         <v>41</v>
       </c>
       <c r="F24">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="G24">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H24">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="J24" t="s">
         <v>76</v>
@@ -1528,10 +1528,10 @@
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A25">
-        <v>887.14900000000011</v>
+        <v>881.87900000000013</v>
       </c>
       <c r="B25">
-        <v>-52.519999999999982</v>
+        <v>-57.789999999999964</v>
       </c>
       <c r="C25" t="s">
         <v>77</v>
@@ -1540,16 +1540,16 @@
         <v>78</v>
       </c>
       <c r="E25">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F25">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="G25">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H25">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="J25" t="s">
         <v>79</v>
@@ -1560,10 +1560,10 @@
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A26">
-        <v>881.87900000000013</v>
+        <v>878.62900000000013</v>
       </c>
       <c r="B26">
-        <v>-57.789999999999964</v>
+        <v>-61.039999999999964</v>
       </c>
       <c r="C26" t="s">
         <v>80</v>
@@ -1575,13 +1575,13 @@
         <v>42</v>
       </c>
       <c r="F26">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G26">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H26">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="J26" t="s">
         <v>82</v>
@@ -1592,10 +1592,10 @@
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A27">
-        <v>878.62900000000013</v>
+        <v>849.52900000000011</v>
       </c>
       <c r="B27">
-        <v>-61.039999999999964</v>
+        <v>-90.139999999999986</v>
       </c>
       <c r="C27" t="s">
         <v>83</v>
@@ -1607,13 +1607,13 @@
         <v>42</v>
       </c>
       <c r="F27">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="G27">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="H27">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="J27" t="s">
         <v>85</v>
